--- a/dados/SURVEY_BRAM_D1.xlsx
+++ b/dados/SURVEY_BRAM_D1.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cefetrjbr-my.sharepoint.com/personal/12396387790_cefet-rj_br/Documents/Empresas e entrevistas/projeto logistica offshore/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cefetrjbr-my.sharepoint.com/personal/12396387790_cefet-rj_br/Documents/Empresas e entrevistas/projeto logistica offshore/ofi/dados/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="75" documentId="11_ED7E539D1D56D6BE346CA07F25318F9C401381BC" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DFAB5CED-7E3A-4A21-BDEC-28C8CF394CDD}"/>
+  <xr:revisionPtr revIDLastSave="25" documentId="11_7149B67CF443AA6B787258010291ED2A03305265" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D8711189-CEBF-4F27-A094-A4A96D6A2900}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="12336" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="BRAM ATLAS" sheetId="1" r:id="rId1"/>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="541" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="915" uniqueCount="82">
   <si>
     <t>data_consulta</t>
   </si>
@@ -120,10 +120,16 @@
     <t>Restricted Manoeuvrability</t>
   </si>
   <si>
-    <t>FPSO ALEXNDRE GUSMÃO</t>
+    <t>FPSO MARECHAL DUQUE DE CAXIAS</t>
   </si>
   <si>
-    <t>mero</t>
+    <t>libra</t>
+  </si>
+  <si>
+    <t>Underway using Engine</t>
+  </si>
+  <si>
+    <t>p-79</t>
   </si>
   <si>
     <t>under using engine</t>
@@ -135,9 +141,6 @@
     <t>tartaruga verde</t>
   </si>
   <si>
-    <t>Underway using Engine</t>
-  </si>
-  <si>
     <t>PETROBRAS 10000</t>
   </si>
   <si>
@@ -147,22 +150,52 @@
     <t>Stopped</t>
   </si>
   <si>
+    <t>NOV Flexiveis</t>
+  </si>
+  <si>
+    <t>porto açu</t>
+  </si>
+  <si>
+    <t>BR ACX</t>
+  </si>
+  <si>
     <t>MOORED</t>
   </si>
   <si>
     <t>stopped</t>
   </si>
   <si>
+    <t>PETROBRAS 69 (P-69)</t>
+  </si>
+  <si>
+    <t>tupi</t>
+  </si>
+  <si>
     <t>p-75_FSO</t>
   </si>
   <si>
-    <t>manoeuvrabulity</t>
+    <t>At Anchor</t>
   </si>
   <si>
-    <t>BR ACX</t>
+    <t>BR RIO</t>
   </si>
   <si>
-    <t>porto açu</t>
+    <t>bahia de guabanara</t>
+  </si>
+  <si>
+    <t>BR NTR</t>
+  </si>
+  <si>
+    <t>porto niteroi</t>
+  </si>
+  <si>
+    <t>Moored</t>
+  </si>
+  <si>
+    <t>Baker Hughes Planta de Fluídos - Niterói</t>
+  </si>
+  <si>
+    <t>manoeuvrabulity</t>
   </si>
   <si>
     <t>restricted manoeuvrability</t>
@@ -171,19 +204,34 @@
     <t>TechnipFMC Flexiveis</t>
   </si>
   <si>
-    <t>NOV Flexiveis</t>
+    <t>Underway</t>
   </si>
   <si>
-    <t>Moored</t>
+    <t>ODN I (NS41)</t>
   </si>
   <si>
-    <t>Underway</t>
+    <t>PETROBRAS 53 (P-53)</t>
+  </si>
+  <si>
+    <t>PETROBRAS 56 (P-56)</t>
+  </si>
+  <si>
+    <t>Semi-Sub/Produção</t>
+  </si>
+  <si>
+    <t>marlin sul</t>
   </si>
   <si>
     <t>inf</t>
   </si>
   <si>
     <t>almirante barroso_FSO</t>
+  </si>
+  <si>
+    <t>PETROBRAS 71 (P-71)</t>
+  </si>
+  <si>
+    <t>itapu</t>
   </si>
   <si>
     <t xml:space="preserve">DEEPWATER ÁQUILA </t>
@@ -207,28 +255,28 @@
     <t>at anchor</t>
   </si>
   <si>
-    <t>NS 28 (WEST POLARIS)</t>
+    <t>P-74</t>
+  </si>
+  <si>
+    <t>p-77_FSO</t>
+  </si>
+  <si>
+    <t>NS 54 (VALARIS DS 4)</t>
   </si>
   <si>
     <t>exploração desconhecida</t>
   </si>
   <si>
-    <t>P-74</t>
-  </si>
-  <si>
-    <t>almirante tamandaré</t>
-  </si>
-  <si>
-    <t>BR NTR</t>
-  </si>
-  <si>
-    <t>porto niteroi</t>
-  </si>
-  <si>
     <t>ATLANTIC STAR (SS45)</t>
   </si>
   <si>
-    <t>NS 54 (VALARIS DS 4)</t>
+    <t>CIDADE ILHA BELA</t>
+  </si>
+  <si>
+    <t>sapinhoá</t>
+  </si>
+  <si>
+    <t>CIDADE SÃO PAULO</t>
   </si>
   <si>
     <t>PETROBRAS 43 (P-43)</t>
@@ -243,22 +291,7 @@
     <t>FPSO SEPETIBA</t>
   </si>
   <si>
-    <t>Baker Hughes Planta de Fluídos - Niterói</t>
-  </si>
-  <si>
-    <t>p-79</t>
-  </si>
-  <si>
-    <t>p-77_FSO</t>
-  </si>
-  <si>
-    <t>At Anchor</t>
-  </si>
-  <si>
-    <t>BR RIO</t>
-  </si>
-  <si>
-    <t>bahia de guabanara</t>
+    <t>mero</t>
   </si>
 </sst>
 </file>
@@ -627,16 +660,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:O8"/>
+  <dimension ref="A1:O15"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="19.6640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="15" customWidth="1"/>
-    <col min="3" max="3" width="19.6640625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="21.88671875" customWidth="1"/>
-    <col min="11" max="11" width="17.33203125" customWidth="1"/>
-    <col min="12" max="12" width="17.44140625" customWidth="1"/>
-    <col min="15" max="15" width="21.109375" customWidth="1"/>
+    <col min="1" max="1" width="21.5546875" customWidth="1"/>
+    <col min="2" max="2" width="18.88671875" customWidth="1"/>
+    <col min="3" max="3" width="22.33203125" customWidth="1"/>
+    <col min="7" max="7" width="14.44140625" customWidth="1"/>
+    <col min="8" max="8" width="16.77734375" customWidth="1"/>
+    <col min="9" max="9" width="18.5546875" customWidth="1"/>
+    <col min="10" max="10" width="24.21875" customWidth="1"/>
+    <col min="11" max="11" width="20.88671875" customWidth="1"/>
+    <col min="12" max="12" width="16.88671875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:15" x14ac:dyDescent="0.3">
@@ -826,7 +861,7 @@
         <v>23</v>
       </c>
       <c r="K5">
-        <v>29.172999999999998</v>
+        <v>29.36</v>
       </c>
       <c r="L5" t="s">
         <v>24</v>
@@ -980,6 +1015,311 @@
       </c>
       <c r="O8" s="3">
         <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A9" s="2">
+        <v>46226.9</v>
+      </c>
+      <c r="B9" s="3">
+        <v>0.54722222222222228</v>
+      </c>
+      <c r="C9" s="2">
+        <v>46226.480555555558</v>
+      </c>
+      <c r="D9">
+        <v>0.06</v>
+      </c>
+      <c r="E9">
+        <v>13.133333333333329</v>
+      </c>
+      <c r="F9" s="3">
+        <v>0.1277777777777778</v>
+      </c>
+      <c r="G9">
+        <v>3.0666666666666669</v>
+      </c>
+      <c r="H9">
+        <v>0.02</v>
+      </c>
+      <c r="I9">
+        <v>0.01</v>
+      </c>
+      <c r="J9" t="s">
+        <v>23</v>
+      </c>
+      <c r="K9">
+        <v>4.5380000000000003</v>
+      </c>
+      <c r="L9" t="s">
+        <v>20</v>
+      </c>
+      <c r="M9" t="s">
+        <v>21</v>
+      </c>
+      <c r="N9" t="s">
+        <v>22</v>
+      </c>
+      <c r="O9" s="3">
+        <v>0.41944444444444451</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A10" s="2">
+        <v>46227.289583333331</v>
+      </c>
+      <c r="B10" s="3">
+        <v>0.38958333333333328</v>
+      </c>
+      <c r="C10" s="2">
+        <v>46226.480555555558</v>
+      </c>
+      <c r="D10">
+        <v>0</v>
+      </c>
+      <c r="E10">
+        <v>9.35</v>
+      </c>
+      <c r="F10" s="3">
+        <v>0</v>
+      </c>
+      <c r="G10">
+        <v>0</v>
+      </c>
+      <c r="J10" t="s">
+        <v>23</v>
+      </c>
+      <c r="K10">
+        <v>4.5380000000000003</v>
+      </c>
+      <c r="L10" t="s">
+        <v>20</v>
+      </c>
+      <c r="M10" t="s">
+        <v>21</v>
+      </c>
+      <c r="N10" t="s">
+        <v>22</v>
+      </c>
+      <c r="O10" s="3">
+        <v>0.80902777777777779</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A11" s="2">
+        <v>46227.886805555558</v>
+      </c>
+      <c r="B11" s="3">
+        <v>0.59722222222222221</v>
+      </c>
+      <c r="C11" s="2">
+        <v>46226.480555555558</v>
+      </c>
+      <c r="D11">
+        <v>0</v>
+      </c>
+      <c r="E11">
+        <v>14.33333333333333</v>
+      </c>
+      <c r="F11" s="3">
+        <v>0</v>
+      </c>
+      <c r="G11">
+        <v>0</v>
+      </c>
+      <c r="J11" t="s">
+        <v>23</v>
+      </c>
+      <c r="K11">
+        <v>4.5380000000000003</v>
+      </c>
+      <c r="L11" t="s">
+        <v>20</v>
+      </c>
+      <c r="M11" t="s">
+        <v>21</v>
+      </c>
+      <c r="N11" t="s">
+        <v>22</v>
+      </c>
+      <c r="O11" s="3">
+        <v>1.40625</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A12" s="2">
+        <v>46228.268055555563</v>
+      </c>
+      <c r="B12" s="3">
+        <v>0.38124999999999998</v>
+      </c>
+      <c r="C12" s="2">
+        <v>46226.480555555558</v>
+      </c>
+      <c r="D12">
+        <v>0</v>
+      </c>
+      <c r="E12">
+        <v>9.15</v>
+      </c>
+      <c r="F12" s="3">
+        <v>0</v>
+      </c>
+      <c r="G12">
+        <v>0</v>
+      </c>
+      <c r="J12" t="s">
+        <v>23</v>
+      </c>
+      <c r="K12">
+        <v>4.5380000000000003</v>
+      </c>
+      <c r="L12" t="s">
+        <v>20</v>
+      </c>
+      <c r="M12" t="s">
+        <v>21</v>
+      </c>
+      <c r="N12" t="s">
+        <v>22</v>
+      </c>
+      <c r="O12" s="3">
+        <v>1.7875000000000001</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A13" s="2">
+        <v>46229.378472222219</v>
+      </c>
+      <c r="B13" s="3">
+        <v>1.1104166666666671</v>
+      </c>
+      <c r="C13" s="2">
+        <v>46226.480555555558</v>
+      </c>
+      <c r="D13">
+        <v>0</v>
+      </c>
+      <c r="E13">
+        <v>26.65</v>
+      </c>
+      <c r="F13" s="3">
+        <v>0</v>
+      </c>
+      <c r="G13">
+        <v>0</v>
+      </c>
+      <c r="J13" t="s">
+        <v>23</v>
+      </c>
+      <c r="K13">
+        <v>4.5380000000000003</v>
+      </c>
+      <c r="L13" t="s">
+        <v>20</v>
+      </c>
+      <c r="M13" t="s">
+        <v>21</v>
+      </c>
+      <c r="N13" t="s">
+        <v>22</v>
+      </c>
+      <c r="O13" s="3">
+        <v>2.8979166666666671</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A14" s="2">
+        <v>46230.353472222218</v>
+      </c>
+      <c r="B14" s="3">
+        <v>0.97499999999999998</v>
+      </c>
+      <c r="C14" s="2">
+        <v>46230.34652777778</v>
+      </c>
+      <c r="D14">
+        <v>0.27</v>
+      </c>
+      <c r="E14">
+        <v>23.4</v>
+      </c>
+      <c r="F14" s="3">
+        <v>3.8659722222222221</v>
+      </c>
+      <c r="G14">
+        <v>92.783333333333331</v>
+      </c>
+      <c r="H14">
+        <v>0</v>
+      </c>
+      <c r="I14">
+        <v>0</v>
+      </c>
+      <c r="J14" t="s">
+        <v>23</v>
+      </c>
+      <c r="K14">
+        <v>4.6760000000000002</v>
+      </c>
+      <c r="L14" t="s">
+        <v>20</v>
+      </c>
+      <c r="M14" t="s">
+        <v>21</v>
+      </c>
+      <c r="N14" t="s">
+        <v>22</v>
+      </c>
+      <c r="O14" s="3">
+        <v>6.9444444444444441E-3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A15" s="2">
+        <v>46230.865972222222</v>
+      </c>
+      <c r="B15" s="3">
+        <v>0.51249999999999996</v>
+      </c>
+      <c r="C15" s="2">
+        <v>46230.85833333333</v>
+      </c>
+      <c r="D15">
+        <v>23.76</v>
+      </c>
+      <c r="E15">
+        <v>12.3</v>
+      </c>
+      <c r="F15" s="3">
+        <v>0.51180555555555551</v>
+      </c>
+      <c r="G15">
+        <v>12.28333333333333</v>
+      </c>
+      <c r="H15">
+        <v>1.93</v>
+      </c>
+      <c r="I15">
+        <v>1.04</v>
+      </c>
+      <c r="J15" t="s">
+        <v>26</v>
+      </c>
+      <c r="K15">
+        <v>5.1920000000000002</v>
+      </c>
+      <c r="L15" t="s">
+        <v>27</v>
+      </c>
+      <c r="M15" t="s">
+        <v>21</v>
+      </c>
+      <c r="N15" t="s">
+        <v>22</v>
+      </c>
+      <c r="O15" s="3">
+        <v>7.6388888888888886E-3</v>
       </c>
     </row>
   </sheetData>
@@ -989,12 +1329,8 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
-  <dimension ref="A1:O7"/>
+  <dimension ref="A1:O14"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="20.109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="20.109375" bestFit="1" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
@@ -1051,7 +1387,7 @@
         <v>46218</v>
       </c>
       <c r="J2" t="s">
-        <v>51</v>
+        <v>67</v>
       </c>
       <c r="O2" s="3">
         <v>2</v>
@@ -1092,7 +1428,7 @@
         <v>103.252</v>
       </c>
       <c r="L3" t="s">
-        <v>45</v>
+        <v>59</v>
       </c>
       <c r="M3" t="s">
         <v>21</v>
@@ -1133,19 +1469,19 @@
         <v>7.57</v>
       </c>
       <c r="J4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="K4">
-        <v>122.196</v>
+        <v>0.224</v>
       </c>
       <c r="L4" t="s">
-        <v>35</v>
+        <v>74</v>
       </c>
       <c r="M4" t="s">
         <v>21</v>
       </c>
       <c r="N4" t="s">
-        <v>22</v>
+        <v>75</v>
       </c>
       <c r="O4" s="3">
         <v>6.2500000000000003E-3</v>
@@ -1180,19 +1516,19 @@
         <v>0.33</v>
       </c>
       <c r="J5" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="K5">
-        <v>127.90300000000001</v>
+        <v>5.9640000000000004</v>
       </c>
       <c r="L5" t="s">
-        <v>35</v>
+        <v>74</v>
       </c>
       <c r="M5" t="s">
         <v>21</v>
       </c>
       <c r="N5" t="s">
-        <v>22</v>
+        <v>75</v>
       </c>
       <c r="O5" s="3">
         <v>5.555497685185185E-3</v>
@@ -1227,19 +1563,19 @@
         <v>0.44</v>
       </c>
       <c r="J6" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="K6">
-        <v>132.108</v>
+        <v>7.9000000000000001E-2</v>
       </c>
       <c r="L6" t="s">
-        <v>60</v>
+        <v>76</v>
       </c>
       <c r="M6" t="s">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="N6" t="s">
-        <v>54</v>
+        <v>75</v>
       </c>
       <c r="O6" s="3">
         <v>0.15555555555555561</v>
@@ -1274,22 +1610,339 @@
         <v>0</v>
       </c>
       <c r="J7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="K7">
-        <v>132.107</v>
+        <v>0.11600000000000001</v>
       </c>
       <c r="L7" t="s">
-        <v>60</v>
+        <v>76</v>
       </c>
       <c r="M7" t="s">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="N7" t="s">
-        <v>54</v>
+        <v>75</v>
       </c>
       <c r="O7" s="3">
         <v>0.2097222222222222</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A8" s="2">
+        <v>46226.9</v>
+      </c>
+      <c r="B8" s="3">
+        <v>0.54722222222222228</v>
+      </c>
+      <c r="C8" s="2">
+        <v>46226.143055555563</v>
+      </c>
+      <c r="D8">
+        <v>0</v>
+      </c>
+      <c r="E8">
+        <v>13.133333333333329</v>
+      </c>
+      <c r="F8" s="3">
+        <v>0</v>
+      </c>
+      <c r="G8">
+        <v>0</v>
+      </c>
+      <c r="J8" t="s">
+        <v>33</v>
+      </c>
+      <c r="K8">
+        <v>0.11600000000000001</v>
+      </c>
+      <c r="L8" t="s">
+        <v>76</v>
+      </c>
+      <c r="M8" t="s">
+        <v>21</v>
+      </c>
+      <c r="N8" t="s">
+        <v>75</v>
+      </c>
+      <c r="O8" s="3">
+        <v>0.75694444444444442</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A9" s="2">
+        <v>46227.289583333331</v>
+      </c>
+      <c r="B9" s="3">
+        <v>0.38958333333333328</v>
+      </c>
+      <c r="C9" s="2">
+        <v>46227.281944444447</v>
+      </c>
+      <c r="D9">
+        <v>0.79</v>
+      </c>
+      <c r="E9">
+        <v>9.35</v>
+      </c>
+      <c r="F9" s="3">
+        <v>1.1388888888888891</v>
+      </c>
+      <c r="G9">
+        <v>27.333333333333329</v>
+      </c>
+      <c r="H9">
+        <v>0.03</v>
+      </c>
+      <c r="I9">
+        <v>0.02</v>
+      </c>
+      <c r="J9" t="s">
+        <v>33</v>
+      </c>
+      <c r="K9">
+        <v>0.78900000000000003</v>
+      </c>
+      <c r="L9" t="s">
+        <v>76</v>
+      </c>
+      <c r="M9" t="s">
+        <v>21</v>
+      </c>
+      <c r="N9" t="s">
+        <v>75</v>
+      </c>
+      <c r="O9" s="3">
+        <v>7.6388888888888886E-3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A10" s="2">
+        <v>46227.886805555558</v>
+      </c>
+      <c r="B10" s="3">
+        <v>0.59722222222222221</v>
+      </c>
+      <c r="C10" s="2">
+        <v>46227.468055555553</v>
+      </c>
+      <c r="D10">
+        <v>1.27</v>
+      </c>
+      <c r="E10">
+        <v>14.33333333333333</v>
+      </c>
+      <c r="F10" s="3">
+        <v>0.18611111111111109</v>
+      </c>
+      <c r="G10">
+        <v>4.4666666666666668</v>
+      </c>
+      <c r="H10">
+        <v>0.28000000000000003</v>
+      </c>
+      <c r="I10">
+        <v>0.15</v>
+      </c>
+      <c r="J10" t="s">
+        <v>33</v>
+      </c>
+      <c r="K10">
+        <v>0.999</v>
+      </c>
+      <c r="L10" t="s">
+        <v>76</v>
+      </c>
+      <c r="M10" t="s">
+        <v>21</v>
+      </c>
+      <c r="N10" t="s">
+        <v>75</v>
+      </c>
+      <c r="O10" s="3">
+        <v>0.41875000000000001</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A11" s="2">
+        <v>46228.268055555563</v>
+      </c>
+      <c r="B11" s="3">
+        <v>0.38124999999999998</v>
+      </c>
+      <c r="C11" s="2">
+        <v>46227.468055555553</v>
+      </c>
+      <c r="D11">
+        <v>0</v>
+      </c>
+      <c r="E11">
+        <v>9.15</v>
+      </c>
+      <c r="F11" s="3">
+        <v>0</v>
+      </c>
+      <c r="G11">
+        <v>0</v>
+      </c>
+      <c r="J11" t="s">
+        <v>33</v>
+      </c>
+      <c r="K11">
+        <v>0.999</v>
+      </c>
+      <c r="L11" t="s">
+        <v>76</v>
+      </c>
+      <c r="M11" t="s">
+        <v>21</v>
+      </c>
+      <c r="N11" t="s">
+        <v>75</v>
+      </c>
+      <c r="O11" s="3">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A12" s="2">
+        <v>46229.378472222219</v>
+      </c>
+      <c r="B12" s="3">
+        <v>1.1104166666666671</v>
+      </c>
+      <c r="C12" s="2">
+        <v>46229.375</v>
+      </c>
+      <c r="D12">
+        <v>328.14</v>
+      </c>
+      <c r="E12">
+        <v>26.65</v>
+      </c>
+      <c r="F12" s="3">
+        <v>1.906944444444445</v>
+      </c>
+      <c r="G12">
+        <v>45.766666666666673</v>
+      </c>
+      <c r="H12">
+        <v>7.17</v>
+      </c>
+      <c r="I12">
+        <v>3.87</v>
+      </c>
+      <c r="J12" t="s">
+        <v>42</v>
+      </c>
+      <c r="K12">
+        <v>3.18</v>
+      </c>
+      <c r="L12" t="s">
+        <v>43</v>
+      </c>
+      <c r="M12" t="s">
+        <v>17</v>
+      </c>
+      <c r="N12" t="s">
+        <v>44</v>
+      </c>
+      <c r="O12" s="3">
+        <v>3.472222222222222E-3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A13" s="2">
+        <v>46230.353472222218</v>
+      </c>
+      <c r="B13" s="3">
+        <v>0.97499999999999998</v>
+      </c>
+      <c r="C13" s="2">
+        <v>46230.352083333331</v>
+      </c>
+      <c r="D13">
+        <v>6.35</v>
+      </c>
+      <c r="E13">
+        <v>23.4</v>
+      </c>
+      <c r="F13" s="3">
+        <v>0.9770833333333333</v>
+      </c>
+      <c r="G13">
+        <v>23.45</v>
+      </c>
+      <c r="H13">
+        <v>0.27</v>
+      </c>
+      <c r="I13">
+        <v>0.15</v>
+      </c>
+      <c r="J13" t="s">
+        <v>47</v>
+      </c>
+      <c r="K13">
+        <v>4.2999999999999997E-2</v>
+      </c>
+      <c r="L13" t="s">
+        <v>16</v>
+      </c>
+      <c r="M13" t="s">
+        <v>17</v>
+      </c>
+      <c r="N13" t="s">
+        <v>18</v>
+      </c>
+      <c r="O13" s="3">
+        <v>1.3888888888888889E-3</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A14" s="2">
+        <v>46230.865972222222</v>
+      </c>
+      <c r="B14" s="3">
+        <v>0.51249999999999996</v>
+      </c>
+      <c r="C14" s="2">
+        <v>46230.859027777777</v>
+      </c>
+      <c r="D14">
+        <v>86.19</v>
+      </c>
+      <c r="E14">
+        <v>12.3</v>
+      </c>
+      <c r="F14" s="3">
+        <v>0.50694444444444442</v>
+      </c>
+      <c r="G14">
+        <v>12.16666666666667</v>
+      </c>
+      <c r="H14">
+        <v>7.08</v>
+      </c>
+      <c r="I14">
+        <v>3.82</v>
+      </c>
+      <c r="J14" t="s">
+        <v>26</v>
+      </c>
+      <c r="K14">
+        <v>85.771000000000001</v>
+      </c>
+      <c r="L14" t="s">
+        <v>48</v>
+      </c>
+      <c r="M14" t="s">
+        <v>17</v>
+      </c>
+      <c r="N14" t="s">
+        <v>46</v>
+      </c>
+      <c r="O14" s="3">
+        <v>6.9444444444444441E-3</v>
       </c>
     </row>
   </sheetData>
@@ -1299,13 +1952,8 @@
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
-  <dimension ref="A1:O7"/>
+  <dimension ref="A1:O14"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="19.77734375" customWidth="1"/>
-    <col min="3" max="3" width="23" customWidth="1"/>
-    <col min="14" max="14" width="12.77734375" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
@@ -1362,7 +2010,7 @@
         <v>46215</v>
       </c>
       <c r="J2" t="s">
-        <v>39</v>
+        <v>50</v>
       </c>
       <c r="O2" s="3">
         <v>5</v>
@@ -1403,7 +2051,7 @@
         <v>12.663</v>
       </c>
       <c r="L3" t="s">
-        <v>61</v>
+        <v>77</v>
       </c>
       <c r="M3" t="s">
         <v>21</v>
@@ -1447,7 +2095,7 @@
         <v>48.145000000000003</v>
       </c>
       <c r="L4" t="s">
-        <v>61</v>
+        <v>77</v>
       </c>
       <c r="M4" t="s">
         <v>21</v>
@@ -1491,13 +2139,13 @@
         <v>3.2229999999999999</v>
       </c>
       <c r="L5" t="s">
-        <v>62</v>
+        <v>78</v>
       </c>
       <c r="M5" t="s">
         <v>17</v>
       </c>
       <c r="N5" t="s">
-        <v>63</v>
+        <v>79</v>
       </c>
       <c r="O5" s="3">
         <v>2.0833333333333329E-3</v>
@@ -1532,19 +2180,19 @@
         <v>0.11</v>
       </c>
       <c r="J6" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="K6">
         <v>0.16700000000000001</v>
       </c>
       <c r="L6" t="s">
-        <v>62</v>
+        <v>78</v>
       </c>
       <c r="M6" t="s">
         <v>17</v>
       </c>
       <c r="N6" t="s">
-        <v>63</v>
+        <v>79</v>
       </c>
       <c r="O6" s="3">
         <v>0</v>
@@ -1579,22 +2227,315 @@
         <v>0</v>
       </c>
       <c r="J7" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="K7">
         <v>0.16500000000000001</v>
       </c>
       <c r="L7" t="s">
-        <v>62</v>
+        <v>78</v>
       </c>
       <c r="M7" t="s">
         <v>17</v>
       </c>
       <c r="N7" t="s">
-        <v>63</v>
+        <v>79</v>
       </c>
       <c r="O7" s="3">
         <v>6.2500000000000003E-3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A8" s="2">
+        <v>46226.882638888892</v>
+      </c>
+      <c r="B8" s="3">
+        <v>0.52430555555555558</v>
+      </c>
+      <c r="C8" s="2">
+        <v>46226.459027777782</v>
+      </c>
+      <c r="D8">
+        <v>5.64</v>
+      </c>
+      <c r="E8">
+        <v>12.58333333333333</v>
+      </c>
+      <c r="F8" s="3">
+        <v>0.1069444444444444</v>
+      </c>
+      <c r="G8">
+        <v>2.5666666666666669</v>
+      </c>
+      <c r="H8">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="I8">
+        <v>1.19</v>
+      </c>
+      <c r="J8" t="s">
+        <v>26</v>
+      </c>
+      <c r="K8">
+        <v>5.5659999999999998</v>
+      </c>
+      <c r="L8" t="s">
+        <v>78</v>
+      </c>
+      <c r="M8" t="s">
+        <v>17</v>
+      </c>
+      <c r="N8" t="s">
+        <v>79</v>
+      </c>
+      <c r="O8" s="3">
+        <v>0.4236111111111111</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A9" s="2">
+        <v>46227.293055555558</v>
+      </c>
+      <c r="B9" s="3">
+        <v>0.41041666666666671</v>
+      </c>
+      <c r="C9" s="2">
+        <v>46226.459027777782</v>
+      </c>
+      <c r="D9">
+        <v>0</v>
+      </c>
+      <c r="E9">
+        <v>9.85</v>
+      </c>
+      <c r="F9" s="3">
+        <v>0</v>
+      </c>
+      <c r="G9">
+        <v>0</v>
+      </c>
+      <c r="J9" t="s">
+        <v>26</v>
+      </c>
+      <c r="K9">
+        <v>5.5659999999999998</v>
+      </c>
+      <c r="L9" t="s">
+        <v>78</v>
+      </c>
+      <c r="M9" t="s">
+        <v>17</v>
+      </c>
+      <c r="N9" t="s">
+        <v>79</v>
+      </c>
+      <c r="O9" s="3">
+        <v>0.83402777777777781</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A10" s="2">
+        <v>46227.881249999999</v>
+      </c>
+      <c r="B10" s="3">
+        <v>0.58819444444444446</v>
+      </c>
+      <c r="C10" s="2">
+        <v>46226.459027777782</v>
+      </c>
+      <c r="D10">
+        <v>0</v>
+      </c>
+      <c r="E10">
+        <v>14.116666666666671</v>
+      </c>
+      <c r="F10" s="3">
+        <v>0</v>
+      </c>
+      <c r="G10">
+        <v>0</v>
+      </c>
+      <c r="J10" t="s">
+        <v>26</v>
+      </c>
+      <c r="K10">
+        <v>5.5659999999999998</v>
+      </c>
+      <c r="L10" t="s">
+        <v>78</v>
+      </c>
+      <c r="M10" t="s">
+        <v>17</v>
+      </c>
+      <c r="N10" t="s">
+        <v>79</v>
+      </c>
+      <c r="O10" s="3">
+        <v>1.4222222222222221</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A11" s="2">
+        <v>46228.268055555563</v>
+      </c>
+      <c r="B11" s="3">
+        <v>0.38680555555555562</v>
+      </c>
+      <c r="C11" s="2">
+        <v>46226.459027777782</v>
+      </c>
+      <c r="D11">
+        <v>0</v>
+      </c>
+      <c r="E11">
+        <v>9.2833333333333332</v>
+      </c>
+      <c r="F11" s="3">
+        <v>0</v>
+      </c>
+      <c r="G11">
+        <v>0</v>
+      </c>
+      <c r="J11" t="s">
+        <v>26</v>
+      </c>
+      <c r="K11">
+        <v>5.5659999999999998</v>
+      </c>
+      <c r="L11" t="s">
+        <v>78</v>
+      </c>
+      <c r="M11" t="s">
+        <v>17</v>
+      </c>
+      <c r="N11" t="s">
+        <v>79</v>
+      </c>
+      <c r="O11" s="3">
+        <v>1.8090277777777779</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A12" s="2">
+        <v>46229.375</v>
+      </c>
+      <c r="B12" s="3">
+        <v>1.106944444444445</v>
+      </c>
+      <c r="C12" s="2">
+        <v>46226.459027777782</v>
+      </c>
+      <c r="D12">
+        <v>0</v>
+      </c>
+      <c r="E12">
+        <v>26.56666666666667</v>
+      </c>
+      <c r="F12" s="3">
+        <v>0</v>
+      </c>
+      <c r="G12">
+        <v>0</v>
+      </c>
+      <c r="J12" t="s">
+        <v>26</v>
+      </c>
+      <c r="K12">
+        <v>5.5659999999999998</v>
+      </c>
+      <c r="L12" t="s">
+        <v>78</v>
+      </c>
+      <c r="M12" t="s">
+        <v>17</v>
+      </c>
+      <c r="N12" t="s">
+        <v>79</v>
+      </c>
+      <c r="O12" s="3">
+        <v>2.915972222222222</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A13" s="2">
+        <v>46230.36041666667</v>
+      </c>
+      <c r="B13" s="3">
+        <v>0.98541666666666672</v>
+      </c>
+      <c r="C13" s="2">
+        <v>46226.459027777782</v>
+      </c>
+      <c r="D13">
+        <v>0</v>
+      </c>
+      <c r="E13">
+        <v>23.65</v>
+      </c>
+      <c r="F13" s="3">
+        <v>0</v>
+      </c>
+      <c r="G13">
+        <v>0</v>
+      </c>
+      <c r="J13" t="s">
+        <v>26</v>
+      </c>
+      <c r="K13">
+        <v>5.5659999999999998</v>
+      </c>
+      <c r="L13" t="s">
+        <v>78</v>
+      </c>
+      <c r="M13" t="s">
+        <v>17</v>
+      </c>
+      <c r="N13" t="s">
+        <v>79</v>
+      </c>
+      <c r="O13" s="3">
+        <v>3.901388888888889</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A14" s="2">
+        <v>46230.865972164349</v>
+      </c>
+      <c r="B14" s="3">
+        <v>0.50555549768518526</v>
+      </c>
+      <c r="C14" s="2">
+        <v>46226.459027777782</v>
+      </c>
+      <c r="D14">
+        <v>0</v>
+      </c>
+      <c r="E14">
+        <v>12.133331944444439</v>
+      </c>
+      <c r="F14" s="3">
+        <v>0</v>
+      </c>
+      <c r="G14">
+        <v>0</v>
+      </c>
+      <c r="J14" t="s">
+        <v>26</v>
+      </c>
+      <c r="K14">
+        <v>5.5659999999999998</v>
+      </c>
+      <c r="L14" t="s">
+        <v>78</v>
+      </c>
+      <c r="M14" t="s">
+        <v>17</v>
+      </c>
+      <c r="N14" t="s">
+        <v>79</v>
+      </c>
+      <c r="O14" s="3">
+        <v>4.4069443865740743</v>
       </c>
     </row>
   </sheetData>
@@ -1604,13 +2545,8 @@
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0B00-000000000000}">
-  <dimension ref="A1:O8"/>
+  <dimension ref="A1:O15"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="20.109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="20.109375" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="16.6640625" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
@@ -1667,7 +2603,7 @@
         <v>46219</v>
       </c>
       <c r="J2" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="O2" s="3">
         <v>0</v>
@@ -1696,25 +2632,25 @@
         <v>0</v>
       </c>
       <c r="H3" t="s">
-        <v>44</v>
+        <v>58</v>
       </c>
       <c r="I3" t="s">
-        <v>44</v>
+        <v>58</v>
       </c>
       <c r="J3" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="K3">
         <v>5.07</v>
       </c>
       <c r="L3" t="s">
-        <v>64</v>
+        <v>80</v>
       </c>
       <c r="M3" t="s">
         <v>21</v>
       </c>
       <c r="N3" t="s">
-        <v>25</v>
+        <v>81</v>
       </c>
       <c r="O3" s="3">
         <v>1</v>
@@ -1749,19 +2685,19 @@
         <v>0.01</v>
       </c>
       <c r="J4" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="K4">
         <v>4.508</v>
       </c>
       <c r="L4" t="s">
-        <v>64</v>
+        <v>80</v>
       </c>
       <c r="M4" t="s">
         <v>21</v>
       </c>
       <c r="N4" t="s">
-        <v>25</v>
+        <v>81</v>
       </c>
       <c r="O4" s="3">
         <v>0.58680555555555558</v>
@@ -1796,19 +2732,19 @@
         <v>0.26</v>
       </c>
       <c r="J5" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="K5">
-        <v>6.4480000000000004</v>
+        <v>15.885</v>
       </c>
       <c r="L5" t="s">
-        <v>24</v>
+        <v>80</v>
       </c>
       <c r="M5" t="s">
         <v>21</v>
       </c>
       <c r="N5" t="s">
-        <v>25</v>
+        <v>81</v>
       </c>
       <c r="O5" s="3">
         <v>0.19236111111111109</v>
@@ -1843,19 +2779,19 @@
         <v>6.49</v>
       </c>
       <c r="J6" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="K6">
         <v>32.704999999999998</v>
       </c>
       <c r="L6" t="s">
-        <v>65</v>
+        <v>48</v>
       </c>
       <c r="M6" t="s">
         <v>17</v>
       </c>
       <c r="N6" t="s">
-        <v>58</v>
+        <v>46</v>
       </c>
       <c r="O6" s="3">
         <v>2.7777777777777779E-3</v>
@@ -1890,19 +2826,19 @@
         <v>0.68</v>
       </c>
       <c r="J7" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="K7">
         <v>13.409000000000001</v>
       </c>
       <c r="L7" t="s">
-        <v>65</v>
+        <v>48</v>
       </c>
       <c r="M7" t="s">
         <v>17</v>
       </c>
       <c r="N7" t="s">
-        <v>58</v>
+        <v>46</v>
       </c>
       <c r="O7" s="3">
         <v>-6.9444444444444447E-4</v>
@@ -1937,13 +2873,13 @@
         <v>8.25</v>
       </c>
       <c r="J8" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="K8">
         <v>23.273</v>
       </c>
       <c r="L8" t="s">
-        <v>66</v>
+        <v>27</v>
       </c>
       <c r="M8" t="s">
         <v>21</v>
@@ -1953,6 +2889,323 @@
       </c>
       <c r="O8" s="3">
         <v>1.111111111111111E-2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A9" s="2">
+        <v>46226.882638888892</v>
+      </c>
+      <c r="B9" s="3">
+        <v>0.52430555555555558</v>
+      </c>
+      <c r="C9" s="2">
+        <v>46226.445833333331</v>
+      </c>
+      <c r="D9">
+        <v>37.270000000000003</v>
+      </c>
+      <c r="E9">
+        <v>12.58333333333333</v>
+      </c>
+      <c r="F9" s="3">
+        <v>9.8611111111111108E-2</v>
+      </c>
+      <c r="G9">
+        <v>2.3666666666666671</v>
+      </c>
+      <c r="H9">
+        <v>15.75</v>
+      </c>
+      <c r="I9">
+        <v>8.5</v>
+      </c>
+      <c r="J9" t="s">
+        <v>26</v>
+      </c>
+      <c r="K9">
+        <v>0.73</v>
+      </c>
+      <c r="L9" t="s">
+        <v>80</v>
+      </c>
+      <c r="M9" t="s">
+        <v>21</v>
+      </c>
+      <c r="N9" t="s">
+        <v>81</v>
+      </c>
+      <c r="O9" s="3">
+        <v>0.43680555555555561</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A10" s="2">
+        <v>46227.293055555558</v>
+      </c>
+      <c r="B10" s="3">
+        <v>0.41041666666666671</v>
+      </c>
+      <c r="C10" s="2">
+        <v>46226.445833333331</v>
+      </c>
+      <c r="D10">
+        <v>0</v>
+      </c>
+      <c r="E10">
+        <v>9.85</v>
+      </c>
+      <c r="F10" s="3">
+        <v>0</v>
+      </c>
+      <c r="G10">
+        <v>0</v>
+      </c>
+      <c r="J10" t="s">
+        <v>26</v>
+      </c>
+      <c r="K10">
+        <v>0.73</v>
+      </c>
+      <c r="L10" t="s">
+        <v>80</v>
+      </c>
+      <c r="M10" t="s">
+        <v>21</v>
+      </c>
+      <c r="N10" t="s">
+        <v>81</v>
+      </c>
+      <c r="O10" s="3">
+        <v>0.84722222222222221</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A11" s="2">
+        <v>46227.881249999999</v>
+      </c>
+      <c r="B11" s="3">
+        <v>0.58819444444444446</v>
+      </c>
+      <c r="C11" s="2">
+        <v>46226.445833333331</v>
+      </c>
+      <c r="D11">
+        <v>0</v>
+      </c>
+      <c r="E11">
+        <v>14.116666666666671</v>
+      </c>
+      <c r="F11" s="3">
+        <v>0</v>
+      </c>
+      <c r="G11">
+        <v>0</v>
+      </c>
+      <c r="J11" t="s">
+        <v>26</v>
+      </c>
+      <c r="K11">
+        <v>0.73</v>
+      </c>
+      <c r="L11" t="s">
+        <v>80</v>
+      </c>
+      <c r="M11" t="s">
+        <v>21</v>
+      </c>
+      <c r="N11" t="s">
+        <v>81</v>
+      </c>
+      <c r="O11" s="3">
+        <v>1.435416666666667</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A12" s="2">
+        <v>46228.268055555563</v>
+      </c>
+      <c r="B12" s="3">
+        <v>0.38680555555555562</v>
+      </c>
+      <c r="C12" s="2">
+        <v>46227.974305555559</v>
+      </c>
+      <c r="D12">
+        <v>7.14</v>
+      </c>
+      <c r="E12">
+        <v>9.2833333333333332</v>
+      </c>
+      <c r="F12" s="3">
+        <v>1.528472222222222</v>
+      </c>
+      <c r="G12">
+        <v>36.68333333333333</v>
+      </c>
+      <c r="H12">
+        <v>0.19</v>
+      </c>
+      <c r="I12">
+        <v>0.1</v>
+      </c>
+      <c r="J12" t="s">
+        <v>33</v>
+      </c>
+      <c r="K12">
+        <v>0.156</v>
+      </c>
+      <c r="L12" t="s">
+        <v>24</v>
+      </c>
+      <c r="M12" t="s">
+        <v>21</v>
+      </c>
+      <c r="N12" t="s">
+        <v>25</v>
+      </c>
+      <c r="O12" s="3">
+        <v>0.29375000000000001</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A13" s="2">
+        <v>46229.375</v>
+      </c>
+      <c r="B13" s="3">
+        <v>1.106944444444445</v>
+      </c>
+      <c r="C13" s="2">
+        <v>46229.370138888888</v>
+      </c>
+      <c r="D13">
+        <v>222.28</v>
+      </c>
+      <c r="E13">
+        <v>26.56666666666667</v>
+      </c>
+      <c r="F13" s="3">
+        <v>1.395833333333333</v>
+      </c>
+      <c r="G13">
+        <v>33.5</v>
+      </c>
+      <c r="H13">
+        <v>6.64</v>
+      </c>
+      <c r="I13">
+        <v>3.59</v>
+      </c>
+      <c r="J13" t="s">
+        <v>33</v>
+      </c>
+      <c r="K13">
+        <v>2.8250000000000002</v>
+      </c>
+      <c r="L13" t="s">
+        <v>43</v>
+      </c>
+      <c r="M13" t="s">
+        <v>17</v>
+      </c>
+      <c r="N13" t="s">
+        <v>44</v>
+      </c>
+      <c r="O13" s="3">
+        <v>4.8611111111111112E-3</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A14" s="2">
+        <v>46230.36041666667</v>
+      </c>
+      <c r="B14" s="3">
+        <v>0.98541666666666672</v>
+      </c>
+      <c r="C14" s="2">
+        <v>46230.356944444437</v>
+      </c>
+      <c r="D14">
+        <v>1.87</v>
+      </c>
+      <c r="E14">
+        <v>23.65</v>
+      </c>
+      <c r="F14" s="3">
+        <v>0.9868055555555556</v>
+      </c>
+      <c r="G14">
+        <v>23.68333333333333</v>
+      </c>
+      <c r="H14">
+        <v>0.08</v>
+      </c>
+      <c r="I14">
+        <v>0.04</v>
+      </c>
+      <c r="J14" t="s">
+        <v>42</v>
+      </c>
+      <c r="K14">
+        <v>0.95099999999999996</v>
+      </c>
+      <c r="L14" t="s">
+        <v>43</v>
+      </c>
+      <c r="M14" t="s">
+        <v>17</v>
+      </c>
+      <c r="N14" t="s">
+        <v>44</v>
+      </c>
+      <c r="O14" s="3">
+        <v>3.472222222222222E-3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A15" s="2">
+        <v>46230.865972164349</v>
+      </c>
+      <c r="B15" s="3">
+        <v>0.50555549768518526</v>
+      </c>
+      <c r="C15" s="2">
+        <v>46230.854861111111</v>
+      </c>
+      <c r="D15">
+        <v>0.05</v>
+      </c>
+      <c r="E15">
+        <v>12.133331944444439</v>
+      </c>
+      <c r="F15" s="3">
+        <v>0.49791666666666667</v>
+      </c>
+      <c r="G15">
+        <v>11.95</v>
+      </c>
+      <c r="H15">
+        <v>0</v>
+      </c>
+      <c r="I15">
+        <v>0</v>
+      </c>
+      <c r="J15" t="s">
+        <v>42</v>
+      </c>
+      <c r="K15">
+        <v>0.95799999999999996</v>
+      </c>
+      <c r="L15" t="s">
+        <v>43</v>
+      </c>
+      <c r="M15" t="s">
+        <v>17</v>
+      </c>
+      <c r="N15" t="s">
+        <v>44</v>
+      </c>
+      <c r="O15" s="3">
+        <v>1.1111053240740741E-2</v>
       </c>
     </row>
   </sheetData>
@@ -1962,25 +3215,8 @@
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0C00-000000000000}">
-  <dimension ref="A1:O7"/>
+  <dimension ref="A1:O14"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="20.33203125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="19.5546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="19.88671875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="16.77734375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="22.33203125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="24.5546875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="27.33203125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="20.33203125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="21.5546875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="25.109375" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="25.44140625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="21.5546875" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="16.5546875" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="9" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="27.6640625" bestFit="1" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
@@ -2072,13 +3308,13 @@
         <v>0.8</v>
       </c>
       <c r="J3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="K3">
         <v>0.73899999999999999</v>
       </c>
       <c r="L3" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="M3" t="s">
         <v>21</v>
@@ -2119,13 +3355,13 @@
         <v>0</v>
       </c>
       <c r="J4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="K4">
         <v>0.77900000000000003</v>
       </c>
       <c r="L4" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="M4" t="s">
         <v>21</v>
@@ -2160,13 +3396,13 @@
         <v>0</v>
       </c>
       <c r="J5" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="K5">
         <v>0.77900000000000003</v>
       </c>
       <c r="L5" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="M5" t="s">
         <v>21</v>
@@ -2207,13 +3443,13 @@
         <v>0</v>
       </c>
       <c r="J6" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="K6">
         <v>0.76700000000000002</v>
       </c>
       <c r="L6" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="M6" t="s">
         <v>21</v>
@@ -2254,13 +3490,13 @@
         <v>0.01</v>
       </c>
       <c r="J7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="K7">
         <v>0.69099999999999995</v>
       </c>
       <c r="L7" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="M7" t="s">
         <v>21</v>
@@ -2270,6 +3506,311 @@
       </c>
       <c r="O7" s="3">
         <v>9.5138888888888884E-2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A8" s="2">
+        <v>46226.882638888892</v>
+      </c>
+      <c r="B8" s="3">
+        <v>0.52430555555555558</v>
+      </c>
+      <c r="C8" s="2">
+        <v>46226.421527777777</v>
+      </c>
+      <c r="D8">
+        <v>0.09</v>
+      </c>
+      <c r="E8">
+        <v>12.58333333333333</v>
+      </c>
+      <c r="F8" s="3">
+        <v>0.1583333333333333</v>
+      </c>
+      <c r="G8">
+        <v>3.8</v>
+      </c>
+      <c r="H8">
+        <v>0.02</v>
+      </c>
+      <c r="I8">
+        <v>0.01</v>
+      </c>
+      <c r="J8" t="s">
+        <v>33</v>
+      </c>
+      <c r="K8">
+        <v>0.754</v>
+      </c>
+      <c r="L8" t="s">
+        <v>41</v>
+      </c>
+      <c r="M8" t="s">
+        <v>21</v>
+      </c>
+      <c r="N8" t="s">
+        <v>22</v>
+      </c>
+      <c r="O8" s="3">
+        <v>0.46111111111111108</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A9" s="2">
+        <v>46227.293055555558</v>
+      </c>
+      <c r="B9" s="3">
+        <v>0.41041666666666671</v>
+      </c>
+      <c r="C9" s="2">
+        <v>46226.421527777777</v>
+      </c>
+      <c r="D9">
+        <v>0</v>
+      </c>
+      <c r="E9">
+        <v>9.85</v>
+      </c>
+      <c r="F9" s="3">
+        <v>0</v>
+      </c>
+      <c r="G9">
+        <v>0</v>
+      </c>
+      <c r="J9" t="s">
+        <v>33</v>
+      </c>
+      <c r="K9">
+        <v>0.754</v>
+      </c>
+      <c r="L9" t="s">
+        <v>41</v>
+      </c>
+      <c r="M9" t="s">
+        <v>21</v>
+      </c>
+      <c r="N9" t="s">
+        <v>22</v>
+      </c>
+      <c r="O9" s="3">
+        <v>0.87152777777777779</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A10" s="2">
+        <v>46227.881249999999</v>
+      </c>
+      <c r="B10" s="3">
+        <v>0.58819444444444446</v>
+      </c>
+      <c r="C10" s="2">
+        <v>46226.421527777777</v>
+      </c>
+      <c r="D10">
+        <v>0</v>
+      </c>
+      <c r="E10">
+        <v>14.116666666666671</v>
+      </c>
+      <c r="F10" s="3">
+        <v>0</v>
+      </c>
+      <c r="G10">
+        <v>0</v>
+      </c>
+      <c r="J10" t="s">
+        <v>33</v>
+      </c>
+      <c r="K10">
+        <v>0.754</v>
+      </c>
+      <c r="L10" t="s">
+        <v>41</v>
+      </c>
+      <c r="M10" t="s">
+        <v>21</v>
+      </c>
+      <c r="N10" t="s">
+        <v>22</v>
+      </c>
+      <c r="O10" s="3">
+        <v>1.4597222222222219</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A11" s="2">
+        <v>46228.268055555563</v>
+      </c>
+      <c r="B11" s="3">
+        <v>0.38680555555555562</v>
+      </c>
+      <c r="C11" s="2">
+        <v>46226.421527777777</v>
+      </c>
+      <c r="D11">
+        <v>0</v>
+      </c>
+      <c r="E11">
+        <v>9.2833333333333332</v>
+      </c>
+      <c r="F11" s="3">
+        <v>0</v>
+      </c>
+      <c r="G11">
+        <v>0</v>
+      </c>
+      <c r="J11" t="s">
+        <v>33</v>
+      </c>
+      <c r="K11">
+        <v>0.754</v>
+      </c>
+      <c r="L11" t="s">
+        <v>41</v>
+      </c>
+      <c r="M11" t="s">
+        <v>21</v>
+      </c>
+      <c r="N11" t="s">
+        <v>22</v>
+      </c>
+      <c r="O11" s="3">
+        <v>1.846527777777778</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A12" s="2">
+        <v>46229.375</v>
+      </c>
+      <c r="B12" s="3">
+        <v>1.106944444444445</v>
+      </c>
+      <c r="C12" s="2">
+        <v>46226.421527777777</v>
+      </c>
+      <c r="D12">
+        <v>0</v>
+      </c>
+      <c r="E12">
+        <v>26.56666666666667</v>
+      </c>
+      <c r="F12" s="3">
+        <v>0</v>
+      </c>
+      <c r="G12">
+        <v>0</v>
+      </c>
+      <c r="J12" t="s">
+        <v>33</v>
+      </c>
+      <c r="K12">
+        <v>0.754</v>
+      </c>
+      <c r="L12" t="s">
+        <v>41</v>
+      </c>
+      <c r="M12" t="s">
+        <v>21</v>
+      </c>
+      <c r="N12" t="s">
+        <v>22</v>
+      </c>
+      <c r="O12" s="3">
+        <v>2.9534722222222221</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A13" s="2">
+        <v>46230.36041666667</v>
+      </c>
+      <c r="B13" s="3">
+        <v>0.98541666666666672</v>
+      </c>
+      <c r="C13" s="2">
+        <v>46230.306944444441</v>
+      </c>
+      <c r="D13">
+        <v>20.420000000000002</v>
+      </c>
+      <c r="E13">
+        <v>23.65</v>
+      </c>
+      <c r="F13" s="3">
+        <v>3.885416666666667</v>
+      </c>
+      <c r="G13">
+        <v>93.25</v>
+      </c>
+      <c r="H13">
+        <v>0.22</v>
+      </c>
+      <c r="I13">
+        <v>0.12</v>
+      </c>
+      <c r="J13" t="s">
+        <v>33</v>
+      </c>
+      <c r="K13">
+        <v>3.5150000000000001</v>
+      </c>
+      <c r="L13" t="s">
+        <v>60</v>
+      </c>
+      <c r="M13" t="s">
+        <v>21</v>
+      </c>
+      <c r="N13" t="s">
+        <v>61</v>
+      </c>
+      <c r="O13" s="3">
+        <v>5.347222222222222E-2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A14" s="2">
+        <v>46230.865972164349</v>
+      </c>
+      <c r="B14" s="3">
+        <v>0.50555549768518526</v>
+      </c>
+      <c r="C14" s="2">
+        <v>46230.361111111109</v>
+      </c>
+      <c r="D14">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="E14">
+        <v>12.133331944444439</v>
+      </c>
+      <c r="F14" s="3">
+        <v>5.4166666666666669E-2</v>
+      </c>
+      <c r="G14">
+        <v>1.3</v>
+      </c>
+      <c r="H14">
+        <v>0.05</v>
+      </c>
+      <c r="I14">
+        <v>0.03</v>
+      </c>
+      <c r="J14" t="s">
+        <v>33</v>
+      </c>
+      <c r="K14">
+        <v>3.4609999999999999</v>
+      </c>
+      <c r="L14" t="s">
+        <v>60</v>
+      </c>
+      <c r="M14" t="s">
+        <v>21</v>
+      </c>
+      <c r="N14" t="s">
+        <v>61</v>
+      </c>
+      <c r="O14" s="3">
+        <v>0.50486105324074082</v>
       </c>
     </row>
   </sheetData>
@@ -2279,12 +3820,8 @@
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0D00-000000000000}">
-  <dimension ref="A1:O8"/>
+  <dimension ref="A1:O15"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="20.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="20.33203125" bestFit="1" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
@@ -2341,7 +3878,7 @@
         <v>46217</v>
       </c>
       <c r="J2" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="O2" s="3">
         <v>2</v>
@@ -2370,25 +3907,25 @@
         <v>0</v>
       </c>
       <c r="H3" t="s">
-        <v>44</v>
+        <v>58</v>
       </c>
       <c r="I3" t="s">
-        <v>44</v>
+        <v>58</v>
       </c>
       <c r="J3" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="K3">
-        <v>14.128</v>
+        <v>10.619</v>
       </c>
       <c r="L3" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="M3" t="s">
         <v>21</v>
       </c>
       <c r="N3" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="O3" s="3">
         <v>3</v>
@@ -2429,7 +3966,7 @@
         <v>3.2029999999999998</v>
       </c>
       <c r="L4" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="M4" t="s">
         <v>21</v>
@@ -2476,7 +4013,7 @@
         <v>3.1749999999999998</v>
       </c>
       <c r="L5" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="M5" t="s">
         <v>21</v>
@@ -2517,13 +4054,13 @@
         <v>6.12</v>
       </c>
       <c r="J6" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="K6">
         <v>102.72</v>
       </c>
       <c r="L6" t="s">
-        <v>66</v>
+        <v>27</v>
       </c>
       <c r="M6" t="s">
         <v>21</v>
@@ -2564,19 +4101,19 @@
         <v>3.77</v>
       </c>
       <c r="J7" t="s">
-        <v>68</v>
+        <v>42</v>
       </c>
       <c r="K7">
         <v>1.2909999999999999</v>
       </c>
       <c r="L7" t="s">
-        <v>69</v>
+        <v>43</v>
       </c>
       <c r="M7" t="s">
         <v>17</v>
       </c>
       <c r="N7" t="s">
-        <v>70</v>
+        <v>44</v>
       </c>
       <c r="O7" s="3">
         <v>0</v>
@@ -2611,22 +4148,339 @@
         <v>0</v>
       </c>
       <c r="J8" t="s">
-        <v>68</v>
+        <v>42</v>
       </c>
       <c r="K8">
         <v>1.25</v>
       </c>
       <c r="L8" t="s">
-        <v>69</v>
+        <v>43</v>
       </c>
       <c r="M8" t="s">
         <v>17</v>
       </c>
       <c r="N8" t="s">
-        <v>70</v>
+        <v>44</v>
       </c>
       <c r="O8" s="3">
         <v>6.9444444444444447E-4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A9" s="2">
+        <v>46226.882638888892</v>
+      </c>
+      <c r="B9" s="3">
+        <v>0.52430555555555558</v>
+      </c>
+      <c r="C9" s="2">
+        <v>46226.880555555559</v>
+      </c>
+      <c r="D9">
+        <v>0.05</v>
+      </c>
+      <c r="E9">
+        <v>12.58333333333333</v>
+      </c>
+      <c r="F9" s="3">
+        <v>0.5229166666666667</v>
+      </c>
+      <c r="G9">
+        <v>12.55</v>
+      </c>
+      <c r="H9">
+        <v>0</v>
+      </c>
+      <c r="I9">
+        <v>0</v>
+      </c>
+      <c r="J9" t="s">
+        <v>42</v>
+      </c>
+      <c r="K9">
+        <v>1.204</v>
+      </c>
+      <c r="L9" t="s">
+        <v>43</v>
+      </c>
+      <c r="M9" t="s">
+        <v>17</v>
+      </c>
+      <c r="N9" t="s">
+        <v>44</v>
+      </c>
+      <c r="O9" s="3">
+        <v>2.0833333333333329E-3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A10" s="2">
+        <v>46227.293055555558</v>
+      </c>
+      <c r="B10" s="3">
+        <v>0.41041666666666671</v>
+      </c>
+      <c r="C10" s="2">
+        <v>46227.27847222222</v>
+      </c>
+      <c r="D10">
+        <v>124.51</v>
+      </c>
+      <c r="E10">
+        <v>9.85</v>
+      </c>
+      <c r="F10" s="3">
+        <v>0.39791666666666659</v>
+      </c>
+      <c r="G10">
+        <v>9.5500000000000007</v>
+      </c>
+      <c r="H10">
+        <v>13.04</v>
+      </c>
+      <c r="I10">
+        <v>7.04</v>
+      </c>
+      <c r="J10" t="s">
+        <v>26</v>
+      </c>
+      <c r="K10">
+        <v>75.944999999999993</v>
+      </c>
+      <c r="L10" t="s">
+        <v>27</v>
+      </c>
+      <c r="M10" t="s">
+        <v>21</v>
+      </c>
+      <c r="N10" t="s">
+        <v>22</v>
+      </c>
+      <c r="O10" s="3">
+        <v>1.458333333333333E-2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A11" s="2">
+        <v>46227.881249999999</v>
+      </c>
+      <c r="B11" s="3">
+        <v>0.58819444444444446</v>
+      </c>
+      <c r="C11" s="2">
+        <v>46227.334722222222</v>
+      </c>
+      <c r="D11">
+        <v>25.7</v>
+      </c>
+      <c r="E11">
+        <v>14.116666666666671</v>
+      </c>
+      <c r="F11" s="3">
+        <v>5.6250000000000001E-2</v>
+      </c>
+      <c r="G11">
+        <v>1.35</v>
+      </c>
+      <c r="H11">
+        <v>19.04</v>
+      </c>
+      <c r="I11">
+        <v>10.28</v>
+      </c>
+      <c r="J11" t="s">
+        <v>26</v>
+      </c>
+      <c r="K11">
+        <v>50.244</v>
+      </c>
+      <c r="L11" t="s">
+        <v>27</v>
+      </c>
+      <c r="M11" t="s">
+        <v>21</v>
+      </c>
+      <c r="N11" t="s">
+        <v>22</v>
+      </c>
+      <c r="O11" s="3">
+        <v>0.54652777777777772</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A12" s="2">
+        <v>46228.268055555563</v>
+      </c>
+      <c r="B12" s="3">
+        <v>0.38680555555555562</v>
+      </c>
+      <c r="C12" s="2">
+        <v>46227.334722222222</v>
+      </c>
+      <c r="D12">
+        <v>0</v>
+      </c>
+      <c r="E12">
+        <v>9.2833333333333332</v>
+      </c>
+      <c r="F12" s="3">
+        <v>0</v>
+      </c>
+      <c r="G12">
+        <v>0</v>
+      </c>
+      <c r="J12" t="s">
+        <v>26</v>
+      </c>
+      <c r="K12">
+        <v>50.244</v>
+      </c>
+      <c r="L12" t="s">
+        <v>27</v>
+      </c>
+      <c r="M12" t="s">
+        <v>21</v>
+      </c>
+      <c r="N12" t="s">
+        <v>22</v>
+      </c>
+      <c r="O12" s="3">
+        <v>0.93333333333333335</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A13" s="2">
+        <v>46229.375</v>
+      </c>
+      <c r="B13" s="3">
+        <v>1.106944444444445</v>
+      </c>
+      <c r="C13" s="2">
+        <v>46227.334722222222</v>
+      </c>
+      <c r="D13">
+        <v>0</v>
+      </c>
+      <c r="E13">
+        <v>26.56666666666667</v>
+      </c>
+      <c r="F13" s="3">
+        <v>0</v>
+      </c>
+      <c r="G13">
+        <v>0</v>
+      </c>
+      <c r="J13" t="s">
+        <v>26</v>
+      </c>
+      <c r="K13">
+        <v>50.244</v>
+      </c>
+      <c r="L13" t="s">
+        <v>27</v>
+      </c>
+      <c r="M13" t="s">
+        <v>21</v>
+      </c>
+      <c r="N13" t="s">
+        <v>22</v>
+      </c>
+      <c r="O13" s="3">
+        <v>2.0402777777777779</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A14" s="2">
+        <v>46230.36041666667</v>
+      </c>
+      <c r="B14" s="3">
+        <v>0.98541666666666672</v>
+      </c>
+      <c r="C14" s="2">
+        <v>46230.101388888892</v>
+      </c>
+      <c r="D14">
+        <v>71.58</v>
+      </c>
+      <c r="E14">
+        <v>23.65</v>
+      </c>
+      <c r="F14" s="3">
+        <v>2.7666666666666671</v>
+      </c>
+      <c r="G14">
+        <v>66.400000000000006</v>
+      </c>
+      <c r="H14">
+        <v>1.08</v>
+      </c>
+      <c r="I14">
+        <v>0.57999999999999996</v>
+      </c>
+      <c r="J14" t="s">
+        <v>23</v>
+      </c>
+      <c r="K14">
+        <v>4.9960000000000004</v>
+      </c>
+      <c r="L14" t="s">
+        <v>20</v>
+      </c>
+      <c r="M14" t="s">
+        <v>21</v>
+      </c>
+      <c r="N14" t="s">
+        <v>22</v>
+      </c>
+      <c r="O14" s="3">
+        <v>0.2590277777777778</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A15" s="2">
+        <v>46230.865972164349</v>
+      </c>
+      <c r="B15" s="3">
+        <v>0.50555549768518526</v>
+      </c>
+      <c r="C15" s="2">
+        <v>46230.708333333343</v>
+      </c>
+      <c r="D15">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="E15">
+        <v>12.133331944444439</v>
+      </c>
+      <c r="F15" s="3">
+        <v>0.6069444444444444</v>
+      </c>
+      <c r="G15">
+        <v>14.56666666666667</v>
+      </c>
+      <c r="H15">
+        <v>0</v>
+      </c>
+      <c r="I15">
+        <v>0</v>
+      </c>
+      <c r="J15" t="s">
+        <v>23</v>
+      </c>
+      <c r="K15">
+        <v>4.9619999999999997</v>
+      </c>
+      <c r="L15" t="s">
+        <v>20</v>
+      </c>
+      <c r="M15" t="s">
+        <v>21</v>
+      </c>
+      <c r="N15" t="s">
+        <v>22</v>
+      </c>
+      <c r="O15" s="3">
+        <v>0.1576388310185185</v>
       </c>
     </row>
   </sheetData>
@@ -2636,8 +4490,13 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:O7"/>
+  <dimension ref="A1:O14"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="24.6640625" customWidth="1"/>
+    <col min="3" max="4" width="20.44140625" customWidth="1"/>
+    <col min="11" max="11" width="13.6640625" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
@@ -2694,7 +4553,7 @@
         <v>46219.79583333333</v>
       </c>
       <c r="J2" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="O2" s="3">
         <v>4.2361111111111113E-2</v>
@@ -2735,13 +4594,13 @@
         <v>1.7210000000000001</v>
       </c>
       <c r="L3" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="M3" t="s">
         <v>21</v>
       </c>
       <c r="N3" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="O3" s="3">
         <v>0.67708333333333337</v>
@@ -2776,19 +4635,19 @@
         <v>0.26</v>
       </c>
       <c r="J4" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="K4">
         <v>10.984999999999999</v>
       </c>
       <c r="L4" t="s">
+        <v>31</v>
+      </c>
+      <c r="M4" t="s">
+        <v>32</v>
+      </c>
+      <c r="N4" t="s">
         <v>30</v>
-      </c>
-      <c r="M4" t="s">
-        <v>31</v>
-      </c>
-      <c r="N4" t="s">
-        <v>28</v>
       </c>
       <c r="O4" s="3">
         <v>0.23402777777777781</v>
@@ -2823,19 +4682,19 @@
         <v>1.18</v>
       </c>
       <c r="J5" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="K5">
         <v>1.431</v>
       </c>
       <c r="L5" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="M5" t="s">
         <v>21</v>
       </c>
       <c r="N5" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="O5" s="3">
         <v>0.37222222222222218</v>
@@ -2870,19 +4729,19 @@
         <v>0.03</v>
       </c>
       <c r="J6" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="K6">
         <v>1.954</v>
       </c>
       <c r="L6" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="M6" t="s">
         <v>21</v>
       </c>
       <c r="N6" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="O6" s="3">
         <v>-2.9861111111111109E-2</v>
@@ -2917,22 +4776,345 @@
         <v>0.16</v>
       </c>
       <c r="J7" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="K7">
         <v>3.573</v>
       </c>
       <c r="L7" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="M7" t="s">
         <v>21</v>
       </c>
       <c r="N7" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="O7" s="3">
         <v>-6.9444444444444447E-4</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A8" s="2">
+        <v>46226.9</v>
+      </c>
+      <c r="B8" s="3">
+        <v>0.54722222222222228</v>
+      </c>
+      <c r="C8" s="2">
+        <v>46226.897916666669</v>
+      </c>
+      <c r="D8">
+        <v>121.36</v>
+      </c>
+      <c r="E8">
+        <v>13.133333333333329</v>
+      </c>
+      <c r="F8" s="3">
+        <v>0.5444444444444444</v>
+      </c>
+      <c r="G8">
+        <v>13.06666666666667</v>
+      </c>
+      <c r="H8">
+        <v>9.2899999999999991</v>
+      </c>
+      <c r="I8">
+        <v>5.0199999999999996</v>
+      </c>
+      <c r="J8" t="s">
+        <v>33</v>
+      </c>
+      <c r="K8">
+        <v>0.78500000000000003</v>
+      </c>
+      <c r="L8" t="s">
+        <v>34</v>
+      </c>
+      <c r="M8" t="s">
+        <v>17</v>
+      </c>
+      <c r="N8" t="s">
+        <v>35</v>
+      </c>
+      <c r="O8" s="3">
+        <v>2.0833333333333329E-3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A9" s="2">
+        <v>46227.289583333331</v>
+      </c>
+      <c r="B9" s="3">
+        <v>0.38958333333333328</v>
+      </c>
+      <c r="C9" s="2">
+        <v>46227.287499999999</v>
+      </c>
+      <c r="D9">
+        <v>6.38</v>
+      </c>
+      <c r="E9">
+        <v>9.35</v>
+      </c>
+      <c r="F9" s="3">
+        <v>0.38958333333333328</v>
+      </c>
+      <c r="G9">
+        <v>9.35</v>
+      </c>
+      <c r="H9">
+        <v>0.68</v>
+      </c>
+      <c r="I9">
+        <v>0.37</v>
+      </c>
+      <c r="J9" t="s">
+        <v>26</v>
+      </c>
+      <c r="K9">
+        <v>3.9380000000000002</v>
+      </c>
+      <c r="L9" t="s">
+        <v>36</v>
+      </c>
+      <c r="M9" t="s">
+        <v>17</v>
+      </c>
+      <c r="N9" t="s">
+        <v>35</v>
+      </c>
+      <c r="O9" s="3">
+        <v>2.0833333333333329E-3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A10" s="2">
+        <v>46227.886805555558</v>
+      </c>
+      <c r="B10" s="3">
+        <v>0.59722222222222221</v>
+      </c>
+      <c r="C10" s="2">
+        <v>46227.379861111112</v>
+      </c>
+      <c r="D10">
+        <v>21.08</v>
+      </c>
+      <c r="E10">
+        <v>14.33333333333333</v>
+      </c>
+      <c r="F10" s="3">
+        <v>9.2361111111111116E-2</v>
+      </c>
+      <c r="G10">
+        <v>2.2166666666666668</v>
+      </c>
+      <c r="H10">
+        <v>9.51</v>
+      </c>
+      <c r="I10">
+        <v>5.13</v>
+      </c>
+      <c r="J10" t="s">
+        <v>26</v>
+      </c>
+      <c r="K10">
+        <v>23.783999999999999</v>
+      </c>
+      <c r="L10" t="s">
+        <v>36</v>
+      </c>
+      <c r="M10" t="s">
+        <v>17</v>
+      </c>
+      <c r="N10" t="s">
+        <v>35</v>
+      </c>
+      <c r="O10" s="3">
+        <v>0.50694444444444442</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A11" s="2">
+        <v>46228.268055555563</v>
+      </c>
+      <c r="B11" s="3">
+        <v>0.38124999999999998</v>
+      </c>
+      <c r="C11" s="2">
+        <v>46228.011805555558</v>
+      </c>
+      <c r="D11">
+        <v>111.71</v>
+      </c>
+      <c r="E11">
+        <v>9.15</v>
+      </c>
+      <c r="F11" s="3">
+        <v>0.63194444444444442</v>
+      </c>
+      <c r="G11">
+        <v>15.16666666666667</v>
+      </c>
+      <c r="H11">
+        <v>7.37</v>
+      </c>
+      <c r="I11">
+        <v>3.98</v>
+      </c>
+      <c r="J11" t="s">
+        <v>26</v>
+      </c>
+      <c r="K11">
+        <v>3.1920000000000002</v>
+      </c>
+      <c r="L11" t="s">
+        <v>29</v>
+      </c>
+      <c r="M11" t="s">
+        <v>21</v>
+      </c>
+      <c r="N11" t="s">
+        <v>30</v>
+      </c>
+      <c r="O11" s="3">
+        <v>0.25624999999999998</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A12" s="2">
+        <v>46229.378472222219</v>
+      </c>
+      <c r="B12" s="3">
+        <v>1.1104166666666671</v>
+      </c>
+      <c r="C12" s="2">
+        <v>46228.867361111108</v>
+      </c>
+      <c r="D12">
+        <v>1.23</v>
+      </c>
+      <c r="E12">
+        <v>26.65</v>
+      </c>
+      <c r="F12" s="3">
+        <v>0.85555555555555551</v>
+      </c>
+      <c r="G12">
+        <v>20.533333333333331</v>
+      </c>
+      <c r="H12">
+        <v>0.06</v>
+      </c>
+      <c r="I12">
+        <v>0.03</v>
+      </c>
+      <c r="J12" t="s">
+        <v>33</v>
+      </c>
+      <c r="K12">
+        <v>1.966</v>
+      </c>
+      <c r="L12" t="s">
+        <v>29</v>
+      </c>
+      <c r="M12" t="s">
+        <v>21</v>
+      </c>
+      <c r="N12" t="s">
+        <v>30</v>
+      </c>
+      <c r="O12" s="3">
+        <v>0.51111111111111107</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A13" s="2">
+        <v>46230.353472222218</v>
+      </c>
+      <c r="B13" s="3">
+        <v>0.97499999999999998</v>
+      </c>
+      <c r="C13" s="2">
+        <v>46228.867361111108</v>
+      </c>
+      <c r="D13">
+        <v>0</v>
+      </c>
+      <c r="E13">
+        <v>23.4</v>
+      </c>
+      <c r="F13" s="3">
+        <v>0</v>
+      </c>
+      <c r="G13">
+        <v>0</v>
+      </c>
+      <c r="J13" t="s">
+        <v>33</v>
+      </c>
+      <c r="K13">
+        <v>1.966</v>
+      </c>
+      <c r="L13" t="s">
+        <v>29</v>
+      </c>
+      <c r="M13" t="s">
+        <v>21</v>
+      </c>
+      <c r="N13" t="s">
+        <v>30</v>
+      </c>
+      <c r="O13" s="3">
+        <v>1.4861111111111109</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A14" s="2">
+        <v>46230.865972222222</v>
+      </c>
+      <c r="B14" s="3">
+        <v>0.51249999999999996</v>
+      </c>
+      <c r="C14" s="2">
+        <v>46230.787499999999</v>
+      </c>
+      <c r="D14">
+        <v>1.32</v>
+      </c>
+      <c r="E14">
+        <v>12.3</v>
+      </c>
+      <c r="F14" s="3">
+        <v>1.9201388888888891</v>
+      </c>
+      <c r="G14">
+        <v>46.083333333333343</v>
+      </c>
+      <c r="H14">
+        <v>0.03</v>
+      </c>
+      <c r="I14">
+        <v>0.02</v>
+      </c>
+      <c r="J14" t="s">
+        <v>26</v>
+      </c>
+      <c r="K14">
+        <v>0.82899999999999996</v>
+      </c>
+      <c r="L14" t="s">
+        <v>29</v>
+      </c>
+      <c r="M14" t="s">
+        <v>21</v>
+      </c>
+      <c r="N14" t="s">
+        <v>30</v>
+      </c>
+      <c r="O14" s="3">
+        <v>7.8472222222222221E-2</v>
       </c>
     </row>
   </sheetData>
@@ -2942,13 +5124,8 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:O8"/>
+  <dimension ref="A1:O15"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="26.77734375" customWidth="1"/>
-    <col min="3" max="3" width="21.5546875" customWidth="1"/>
-    <col min="10" max="10" width="14.33203125" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
@@ -3005,7 +5182,7 @@
         <v>46219.845138888893</v>
       </c>
       <c r="J2" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="O2" s="3">
         <v>-2.7777777777777779E-3</v>
@@ -3040,7 +5217,7 @@
         <v>0.26</v>
       </c>
       <c r="J3" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="K3">
         <v>1.4279999999999999</v>
@@ -3090,16 +5267,16 @@
         <v>19</v>
       </c>
       <c r="K4">
-        <v>58.871000000000002</v>
+        <v>47.435000000000002</v>
       </c>
       <c r="L4" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="M4" t="s">
         <v>21</v>
       </c>
       <c r="N4" t="s">
-        <v>22</v>
+        <v>40</v>
       </c>
       <c r="O4" s="3">
         <v>0.4826388888888889</v>
@@ -3134,19 +5311,19 @@
         <v>0.17</v>
       </c>
       <c r="J5" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="K5">
-        <v>54.622</v>
+        <v>54.195999999999998</v>
       </c>
       <c r="L5" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="M5" t="s">
         <v>21</v>
       </c>
       <c r="N5" t="s">
-        <v>22</v>
+        <v>40</v>
       </c>
       <c r="O5" s="3">
         <v>6.805555555555555E-2</v>
@@ -3175,19 +5352,19 @@
         <v>0</v>
       </c>
       <c r="J6" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="K6">
-        <v>54.622</v>
+        <v>54.195999999999998</v>
       </c>
       <c r="L6" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="M6" t="s">
         <v>21</v>
       </c>
       <c r="N6" t="s">
-        <v>22</v>
+        <v>40</v>
       </c>
       <c r="O6" s="3">
         <v>0.45347216435185189</v>
@@ -3222,13 +5399,13 @@
         <v>7.0000000000000007E-2</v>
       </c>
       <c r="J7" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="K7">
         <v>51.95</v>
       </c>
       <c r="L7" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="M7" t="s">
         <v>21</v>
@@ -3269,13 +5446,13 @@
         <v>0</v>
       </c>
       <c r="J8" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="K8">
         <v>51.954000000000001</v>
       </c>
       <c r="L8" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="M8" t="s">
         <v>21</v>
@@ -3285,6 +5462,317 @@
       </c>
       <c r="O8" s="3">
         <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A9" s="2">
+        <v>46226.9</v>
+      </c>
+      <c r="B9" s="3">
+        <v>0.54722222222222228</v>
+      </c>
+      <c r="C9" s="2">
+        <v>46226.369444444441</v>
+      </c>
+      <c r="D9">
+        <v>0</v>
+      </c>
+      <c r="E9">
+        <v>13.133333333333329</v>
+      </c>
+      <c r="F9" s="3">
+        <v>1.666666666666667E-2</v>
+      </c>
+      <c r="G9">
+        <v>0.4</v>
+      </c>
+      <c r="H9">
+        <v>0</v>
+      </c>
+      <c r="I9">
+        <v>0</v>
+      </c>
+      <c r="J9" t="s">
+        <v>33</v>
+      </c>
+      <c r="K9">
+        <v>51.954999999999998</v>
+      </c>
+      <c r="L9" t="s">
+        <v>41</v>
+      </c>
+      <c r="M9" t="s">
+        <v>21</v>
+      </c>
+      <c r="N9" t="s">
+        <v>22</v>
+      </c>
+      <c r="O9" s="3">
+        <v>0.53055555555555556</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A10" s="2">
+        <v>46227.289583333331</v>
+      </c>
+      <c r="B10" s="3">
+        <v>0.38958333333333328</v>
+      </c>
+      <c r="C10" s="2">
+        <v>46226.369444444441</v>
+      </c>
+      <c r="D10">
+        <v>0</v>
+      </c>
+      <c r="E10">
+        <v>9.35</v>
+      </c>
+      <c r="F10" s="3">
+        <v>0</v>
+      </c>
+      <c r="G10">
+        <v>0</v>
+      </c>
+      <c r="J10" t="s">
+        <v>33</v>
+      </c>
+      <c r="K10">
+        <v>51.954999999999998</v>
+      </c>
+      <c r="L10" t="s">
+        <v>41</v>
+      </c>
+      <c r="M10" t="s">
+        <v>21</v>
+      </c>
+      <c r="N10" t="s">
+        <v>22</v>
+      </c>
+      <c r="O10" s="3">
+        <v>0.92013888888888884</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A11" s="2">
+        <v>46227.886805555558</v>
+      </c>
+      <c r="B11" s="3">
+        <v>0.59722222222222221</v>
+      </c>
+      <c r="C11" s="2">
+        <v>46226.369444444441</v>
+      </c>
+      <c r="D11">
+        <v>0</v>
+      </c>
+      <c r="E11">
+        <v>14.33333333333333</v>
+      </c>
+      <c r="F11" s="3">
+        <v>0</v>
+      </c>
+      <c r="G11">
+        <v>0</v>
+      </c>
+      <c r="J11" t="s">
+        <v>33</v>
+      </c>
+      <c r="K11">
+        <v>51.954999999999998</v>
+      </c>
+      <c r="L11" t="s">
+        <v>41</v>
+      </c>
+      <c r="M11" t="s">
+        <v>21</v>
+      </c>
+      <c r="N11" t="s">
+        <v>22</v>
+      </c>
+      <c r="O11" s="3">
+        <v>1.5173611111111109</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A12" s="2">
+        <v>46228.268055555563</v>
+      </c>
+      <c r="B12" s="3">
+        <v>0.38124999999999998</v>
+      </c>
+      <c r="C12" s="2">
+        <v>46226.369444444441</v>
+      </c>
+      <c r="D12">
+        <v>0</v>
+      </c>
+      <c r="E12">
+        <v>9.15</v>
+      </c>
+      <c r="F12" s="3">
+        <v>0</v>
+      </c>
+      <c r="G12">
+        <v>0</v>
+      </c>
+      <c r="J12" t="s">
+        <v>33</v>
+      </c>
+      <c r="K12">
+        <v>51.954999999999998</v>
+      </c>
+      <c r="L12" t="s">
+        <v>41</v>
+      </c>
+      <c r="M12" t="s">
+        <v>21</v>
+      </c>
+      <c r="N12" t="s">
+        <v>22</v>
+      </c>
+      <c r="O12" s="3">
+        <v>1.898611111111111</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A13" s="2">
+        <v>46229.378472222219</v>
+      </c>
+      <c r="B13" s="3">
+        <v>1.1104166666666671</v>
+      </c>
+      <c r="C13" s="2">
+        <v>46229.372916666667</v>
+      </c>
+      <c r="D13">
+        <v>272.82</v>
+      </c>
+      <c r="E13">
+        <v>26.65</v>
+      </c>
+      <c r="F13" s="3">
+        <v>3.0034722222222219</v>
+      </c>
+      <c r="G13">
+        <v>72.083333333333329</v>
+      </c>
+      <c r="H13">
+        <v>3.78</v>
+      </c>
+      <c r="I13">
+        <v>2.04</v>
+      </c>
+      <c r="J13" t="s">
+        <v>42</v>
+      </c>
+      <c r="K13">
+        <v>4.2789999999999999</v>
+      </c>
+      <c r="L13" t="s">
+        <v>43</v>
+      </c>
+      <c r="M13" t="s">
+        <v>17</v>
+      </c>
+      <c r="N13" t="s">
+        <v>44</v>
+      </c>
+      <c r="O13" s="3">
+        <v>5.5555555555555558E-3</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A14" s="2">
+        <v>46230.353472222218</v>
+      </c>
+      <c r="B14" s="3">
+        <v>0.97499999999999998</v>
+      </c>
+      <c r="C14" s="2">
+        <v>46230.351388888892</v>
+      </c>
+      <c r="D14">
+        <v>5.62</v>
+      </c>
+      <c r="E14">
+        <v>23.4</v>
+      </c>
+      <c r="F14" s="3">
+        <v>0.97847222222222219</v>
+      </c>
+      <c r="G14">
+        <v>23.483333333333331</v>
+      </c>
+      <c r="H14">
+        <v>0.24</v>
+      </c>
+      <c r="I14">
+        <v>0.13</v>
+      </c>
+      <c r="J14" t="s">
+        <v>26</v>
+      </c>
+      <c r="K14">
+        <v>0.153</v>
+      </c>
+      <c r="L14" t="s">
+        <v>45</v>
+      </c>
+      <c r="M14" t="s">
+        <v>17</v>
+      </c>
+      <c r="N14" t="s">
+        <v>46</v>
+      </c>
+      <c r="O14" s="3">
+        <v>2.0833333333333329E-3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A15" s="2">
+        <v>46230.865972222222</v>
+      </c>
+      <c r="B15" s="3">
+        <v>0.51249999999999996</v>
+      </c>
+      <c r="C15" s="2">
+        <v>46230.856944444437</v>
+      </c>
+      <c r="D15">
+        <v>0.6</v>
+      </c>
+      <c r="E15">
+        <v>12.3</v>
+      </c>
+      <c r="F15" s="3">
+        <v>0.50555555555555554</v>
+      </c>
+      <c r="G15">
+        <v>12.133333333333329</v>
+      </c>
+      <c r="H15">
+        <v>0.05</v>
+      </c>
+      <c r="I15">
+        <v>0.03</v>
+      </c>
+      <c r="J15" t="s">
+        <v>47</v>
+      </c>
+      <c r="K15">
+        <v>0.109</v>
+      </c>
+      <c r="L15" t="s">
+        <v>48</v>
+      </c>
+      <c r="M15" t="s">
+        <v>17</v>
+      </c>
+      <c r="N15" t="s">
+        <v>46</v>
+      </c>
+      <c r="O15" s="3">
+        <v>9.0277777777777769E-3</v>
       </c>
     </row>
   </sheetData>
@@ -3294,7 +5782,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:O10"/>
+  <dimension ref="A1:O17"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:15" x14ac:dyDescent="0.3">
@@ -3352,7 +5840,7 @@
         <v>46219.802083333343</v>
       </c>
       <c r="J2" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="O2" s="3">
         <v>-6.9444444444444447E-4</v>
@@ -3387,19 +5875,19 @@
         <v>0</v>
       </c>
       <c r="J3" t="s">
-        <v>36</v>
+        <v>49</v>
       </c>
       <c r="K3">
         <v>6.3369999999999997</v>
       </c>
       <c r="L3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="M3" t="s">
         <v>17</v>
       </c>
       <c r="N3" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="O3" s="3">
         <v>1.3888888888888889E-3</v>
@@ -3434,19 +5922,19 @@
         <v>0.09</v>
       </c>
       <c r="J4" t="s">
-        <v>39</v>
+        <v>50</v>
       </c>
       <c r="K4">
         <v>1.393</v>
       </c>
       <c r="L4" t="s">
-        <v>40</v>
+        <v>51</v>
       </c>
       <c r="M4" t="s">
         <v>17</v>
       </c>
       <c r="N4" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="O4" s="3">
         <v>7.6388888888888886E-3</v>
@@ -3487,13 +5975,13 @@
         <v>1.169</v>
       </c>
       <c r="L5" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="M5" t="s">
         <v>17</v>
       </c>
       <c r="N5" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="O5" s="3">
         <v>0.74236111111111114</v>
@@ -3534,13 +6022,13 @@
         <v>0.77900000000000003</v>
       </c>
       <c r="L6" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="M6" t="s">
         <v>17</v>
       </c>
       <c r="N6" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="O6" s="3">
         <v>0</v>
@@ -3581,13 +6069,13 @@
         <v>1.63</v>
       </c>
       <c r="L7" t="s">
-        <v>40</v>
+        <v>51</v>
       </c>
       <c r="M7" t="s">
         <v>17</v>
       </c>
       <c r="N7" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="O7" s="3">
         <v>2.0833333333333329E-3</v>
@@ -3622,19 +6110,19 @@
         <v>0.13</v>
       </c>
       <c r="J8" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="K8">
         <v>0.80800000000000005</v>
       </c>
       <c r="L8" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="M8" t="s">
         <v>17</v>
       </c>
       <c r="N8" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="O8" s="3">
         <v>4.1666087962962967E-3</v>
@@ -3669,19 +6157,19 @@
         <v>0.01</v>
       </c>
       <c r="J9" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="K9">
         <v>0.55000000000000004</v>
       </c>
       <c r="L9" t="s">
-        <v>40</v>
+        <v>51</v>
       </c>
       <c r="M9" t="s">
         <v>17</v>
       </c>
       <c r="N9" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="O9" s="3">
         <v>-5.1388888888888887E-2</v>
@@ -3716,22 +6204,327 @@
         <v>4.99</v>
       </c>
       <c r="J10" t="s">
-        <v>43</v>
+        <v>52</v>
       </c>
       <c r="K10">
         <v>27.901</v>
       </c>
       <c r="L10" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="M10" t="s">
         <v>21</v>
       </c>
       <c r="N10" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="O10" s="3">
         <v>2.7777777777777779E-3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A11" s="2">
+        <v>46226.9</v>
+      </c>
+      <c r="B11" s="3">
+        <v>0.54722222222222228</v>
+      </c>
+      <c r="C11" s="2">
+        <v>46226.887499999997</v>
+      </c>
+      <c r="D11">
+        <v>77.83</v>
+      </c>
+      <c r="E11">
+        <v>13.133333333333329</v>
+      </c>
+      <c r="F11" s="3">
+        <v>0.53749999999999998</v>
+      </c>
+      <c r="G11">
+        <v>12.9</v>
+      </c>
+      <c r="H11">
+        <v>6.03</v>
+      </c>
+      <c r="I11">
+        <v>3.26</v>
+      </c>
+      <c r="J11" t="s">
+        <v>47</v>
+      </c>
+      <c r="K11">
+        <v>3.996</v>
+      </c>
+      <c r="L11" t="s">
+        <v>53</v>
+      </c>
+      <c r="M11" t="s">
+        <v>32</v>
+      </c>
+      <c r="O11" s="3">
+        <v>1.2500000000000001E-2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A12" s="2">
+        <v>46227.289583333331</v>
+      </c>
+      <c r="B12" s="3">
+        <v>0.38958333333333328</v>
+      </c>
+      <c r="C12" s="2">
+        <v>46227.26666666667</v>
+      </c>
+      <c r="D12">
+        <v>5.2</v>
+      </c>
+      <c r="E12">
+        <v>9.35</v>
+      </c>
+      <c r="F12" s="3">
+        <v>0.37916666666666671</v>
+      </c>
+      <c r="G12">
+        <v>9.1</v>
+      </c>
+      <c r="H12">
+        <v>0.56999999999999995</v>
+      </c>
+      <c r="I12">
+        <v>0.31</v>
+      </c>
+      <c r="J12" t="s">
+        <v>52</v>
+      </c>
+      <c r="K12">
+        <v>4.6050000000000004</v>
+      </c>
+      <c r="L12" t="s">
+        <v>53</v>
+      </c>
+      <c r="M12" t="s">
+        <v>32</v>
+      </c>
+      <c r="O12" s="3">
+        <v>2.2916666666666669E-2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A13" s="2">
+        <v>46227.886805555558</v>
+      </c>
+      <c r="B13" s="3">
+        <v>0.59722222222222221</v>
+      </c>
+      <c r="C13" s="2">
+        <v>46227.804166666669</v>
+      </c>
+      <c r="D13">
+        <v>5.16</v>
+      </c>
+      <c r="E13">
+        <v>14.33333333333333</v>
+      </c>
+      <c r="F13" s="3">
+        <v>0.53749999999999998</v>
+      </c>
+      <c r="G13">
+        <v>12.9</v>
+      </c>
+      <c r="H13">
+        <v>0.4</v>
+      </c>
+      <c r="I13">
+        <v>0.22</v>
+      </c>
+      <c r="J13" t="s">
+        <v>47</v>
+      </c>
+      <c r="K13">
+        <v>3.9689999999999999</v>
+      </c>
+      <c r="L13" t="s">
+        <v>53</v>
+      </c>
+      <c r="M13" t="s">
+        <v>32</v>
+      </c>
+      <c r="O13" s="3">
+        <v>8.2638888888888887E-2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A14" s="2">
+        <v>46228.268055555563</v>
+      </c>
+      <c r="B14" s="3">
+        <v>0.38124999999999998</v>
+      </c>
+      <c r="C14" s="2">
+        <v>46227.804166666669</v>
+      </c>
+      <c r="D14">
+        <v>0</v>
+      </c>
+      <c r="E14">
+        <v>9.15</v>
+      </c>
+      <c r="F14" s="3">
+        <v>0</v>
+      </c>
+      <c r="G14">
+        <v>0</v>
+      </c>
+      <c r="J14" t="s">
+        <v>47</v>
+      </c>
+      <c r="K14">
+        <v>3.9689999999999999</v>
+      </c>
+      <c r="L14" t="s">
+        <v>53</v>
+      </c>
+      <c r="M14" t="s">
+        <v>32</v>
+      </c>
+      <c r="O14" s="3">
+        <v>0.46388888888888891</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A15" s="2">
+        <v>46229.378472222219</v>
+      </c>
+      <c r="B15" s="3">
+        <v>1.1104166666666671</v>
+      </c>
+      <c r="C15" s="2">
+        <v>46229.259027777778</v>
+      </c>
+      <c r="D15">
+        <v>7.96</v>
+      </c>
+      <c r="E15">
+        <v>26.65</v>
+      </c>
+      <c r="F15" s="3">
+        <v>1.4548611111111109</v>
+      </c>
+      <c r="G15">
+        <v>34.916666666666657</v>
+      </c>
+      <c r="H15">
+        <v>0.23</v>
+      </c>
+      <c r="I15">
+        <v>0.12</v>
+      </c>
+      <c r="J15" t="s">
+        <v>52</v>
+      </c>
+      <c r="K15">
+        <v>5.1879999999999997</v>
+      </c>
+      <c r="L15" t="s">
+        <v>54</v>
+      </c>
+      <c r="M15" t="s">
+        <v>21</v>
+      </c>
+      <c r="O15" s="3">
+        <v>0.11944444444444451</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A16" s="2">
+        <v>46230.353472222218</v>
+      </c>
+      <c r="B16" s="3">
+        <v>0.97499999999999998</v>
+      </c>
+      <c r="C16" s="2">
+        <v>46230.288194444453</v>
+      </c>
+      <c r="D16">
+        <v>7.97</v>
+      </c>
+      <c r="E16">
+        <v>23.4</v>
+      </c>
+      <c r="F16" s="3">
+        <v>1.029166666666667</v>
+      </c>
+      <c r="G16">
+        <v>24.7</v>
+      </c>
+      <c r="H16">
+        <v>0.32</v>
+      </c>
+      <c r="I16">
+        <v>0.17</v>
+      </c>
+      <c r="J16" t="s">
+        <v>47</v>
+      </c>
+      <c r="K16">
+        <v>4.0590000000000002</v>
+      </c>
+      <c r="L16" t="s">
+        <v>53</v>
+      </c>
+      <c r="M16" t="s">
+        <v>32</v>
+      </c>
+      <c r="O16" s="3">
+        <v>6.5277777777777782E-2</v>
+      </c>
+    </row>
+    <row r="17" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A17" s="2">
+        <v>46230.865972222222</v>
+      </c>
+      <c r="B17" s="3">
+        <v>0.51249999999999996</v>
+      </c>
+      <c r="C17" s="2">
+        <v>46230.804861111108</v>
+      </c>
+      <c r="D17">
+        <v>18.86</v>
+      </c>
+      <c r="E17">
+        <v>12.3</v>
+      </c>
+      <c r="F17" s="3">
+        <v>0.51666666666666672</v>
+      </c>
+      <c r="G17">
+        <v>12.4</v>
+      </c>
+      <c r="H17">
+        <v>1.52</v>
+      </c>
+      <c r="I17">
+        <v>0.82</v>
+      </c>
+      <c r="J17" t="s">
+        <v>52</v>
+      </c>
+      <c r="K17">
+        <v>10.589</v>
+      </c>
+      <c r="L17" t="s">
+        <v>55</v>
+      </c>
+      <c r="M17" t="s">
+        <v>56</v>
+      </c>
+      <c r="N17" t="s">
+        <v>57</v>
+      </c>
+      <c r="O17" s="3">
+        <v>6.1111111111111109E-2</v>
       </c>
     </row>
   </sheetData>
@@ -3741,7 +6534,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:O8"/>
+  <dimension ref="A1:O15"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:15" x14ac:dyDescent="0.3">
@@ -3799,7 +6592,7 @@
         <v>46217.711805555547</v>
       </c>
       <c r="J2" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="O2" s="3">
         <v>2.1965277777777779</v>
@@ -3828,25 +6621,25 @@
         <v>0</v>
       </c>
       <c r="H3" t="s">
-        <v>44</v>
+        <v>58</v>
       </c>
       <c r="I3" t="s">
-        <v>44</v>
+        <v>58</v>
       </c>
       <c r="J3" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="K3">
-        <v>60.121000000000002</v>
+        <v>49.924999999999997</v>
       </c>
       <c r="L3" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="M3" t="s">
         <v>21</v>
       </c>
       <c r="N3" t="s">
-        <v>22</v>
+        <v>40</v>
       </c>
       <c r="O3" s="3">
         <v>2.927777777777778</v>
@@ -3928,13 +6721,13 @@
         <v>4.3600000000000003</v>
       </c>
       <c r="J5" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="K5">
         <v>90.275000000000006</v>
       </c>
       <c r="L5" t="s">
-        <v>45</v>
+        <v>59</v>
       </c>
       <c r="M5" t="s">
         <v>21</v>
@@ -3969,13 +6762,13 @@
         <v>0</v>
       </c>
       <c r="J6" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="K6">
         <v>90.275000000000006</v>
       </c>
       <c r="L6" t="s">
-        <v>45</v>
+        <v>59</v>
       </c>
       <c r="M6" t="s">
         <v>21</v>
@@ -4016,19 +6809,19 @@
         <v>4.91</v>
       </c>
       <c r="J7" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="K7">
-        <v>60.828000000000003</v>
+        <v>39.579000000000001</v>
       </c>
       <c r="L7" t="s">
-        <v>35</v>
+        <v>60</v>
       </c>
       <c r="M7" t="s">
         <v>21</v>
       </c>
       <c r="N7" t="s">
-        <v>22</v>
+        <v>61</v>
       </c>
       <c r="O7" s="3">
         <v>0.53472222222222221</v>
@@ -4057,22 +6850,309 @@
         <v>0</v>
       </c>
       <c r="J8" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="K8">
-        <v>60.828000000000003</v>
+        <v>39.579000000000001</v>
       </c>
       <c r="L8" t="s">
-        <v>35</v>
+        <v>60</v>
       </c>
       <c r="M8" t="s">
         <v>21</v>
       </c>
       <c r="N8" t="s">
-        <v>22</v>
+        <v>61</v>
       </c>
       <c r="O8" s="3">
         <v>1.028472222222222</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A9" s="2">
+        <v>46226.9</v>
+      </c>
+      <c r="B9" s="3">
+        <v>0.54722222222222228</v>
+      </c>
+      <c r="C9" s="2">
+        <v>46225.324305555558</v>
+      </c>
+      <c r="D9">
+        <v>0</v>
+      </c>
+      <c r="E9">
+        <v>13.133333333333329</v>
+      </c>
+      <c r="F9" s="3">
+        <v>0</v>
+      </c>
+      <c r="G9">
+        <v>0</v>
+      </c>
+      <c r="J9" t="s">
+        <v>26</v>
+      </c>
+      <c r="K9">
+        <v>39.579000000000001</v>
+      </c>
+      <c r="L9" t="s">
+        <v>60</v>
+      </c>
+      <c r="M9" t="s">
+        <v>21</v>
+      </c>
+      <c r="N9" t="s">
+        <v>61</v>
+      </c>
+      <c r="O9" s="3">
+        <v>1.575694444444445</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A10" s="2">
+        <v>46227.289583333331</v>
+      </c>
+      <c r="B10" s="3">
+        <v>0.38958333333333328</v>
+      </c>
+      <c r="C10" s="2">
+        <v>46225.324305555558</v>
+      </c>
+      <c r="D10">
+        <v>0</v>
+      </c>
+      <c r="E10">
+        <v>9.35</v>
+      </c>
+      <c r="F10" s="3">
+        <v>0</v>
+      </c>
+      <c r="G10">
+        <v>0</v>
+      </c>
+      <c r="J10" t="s">
+        <v>26</v>
+      </c>
+      <c r="K10">
+        <v>39.579000000000001</v>
+      </c>
+      <c r="L10" t="s">
+        <v>60</v>
+      </c>
+      <c r="M10" t="s">
+        <v>21</v>
+      </c>
+      <c r="N10" t="s">
+        <v>61</v>
+      </c>
+      <c r="O10" s="3">
+        <v>1.9652777777777779</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A11" s="2">
+        <v>46227.886805555558</v>
+      </c>
+      <c r="B11" s="3">
+        <v>0.59722222222222221</v>
+      </c>
+      <c r="C11" s="2">
+        <v>46225.324305555558</v>
+      </c>
+      <c r="D11">
+        <v>0</v>
+      </c>
+      <c r="E11">
+        <v>14.33333333333333</v>
+      </c>
+      <c r="F11" s="3">
+        <v>0</v>
+      </c>
+      <c r="G11">
+        <v>0</v>
+      </c>
+      <c r="J11" t="s">
+        <v>26</v>
+      </c>
+      <c r="K11">
+        <v>39.579000000000001</v>
+      </c>
+      <c r="L11" t="s">
+        <v>60</v>
+      </c>
+      <c r="M11" t="s">
+        <v>21</v>
+      </c>
+      <c r="N11" t="s">
+        <v>61</v>
+      </c>
+      <c r="O11" s="3">
+        <v>2.5625</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A12" s="2">
+        <v>46228.268055555563</v>
+      </c>
+      <c r="B12" s="3">
+        <v>0.38124999999999998</v>
+      </c>
+      <c r="C12" s="2">
+        <v>46225.324305555558</v>
+      </c>
+      <c r="D12">
+        <v>0</v>
+      </c>
+      <c r="E12">
+        <v>9.15</v>
+      </c>
+      <c r="F12" s="3">
+        <v>0</v>
+      </c>
+      <c r="G12">
+        <v>0</v>
+      </c>
+      <c r="J12" t="s">
+        <v>26</v>
+      </c>
+      <c r="K12">
+        <v>39.579000000000001</v>
+      </c>
+      <c r="L12" t="s">
+        <v>60</v>
+      </c>
+      <c r="M12" t="s">
+        <v>21</v>
+      </c>
+      <c r="N12" t="s">
+        <v>61</v>
+      </c>
+      <c r="O12" s="3">
+        <v>2.9437500000000001</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A13" s="2">
+        <v>46229.378472222219</v>
+      </c>
+      <c r="B13" s="3">
+        <v>1.1104166666666671</v>
+      </c>
+      <c r="C13" s="2">
+        <v>46225.324305555558</v>
+      </c>
+      <c r="D13">
+        <v>0</v>
+      </c>
+      <c r="E13">
+        <v>26.65</v>
+      </c>
+      <c r="F13" s="3">
+        <v>0</v>
+      </c>
+      <c r="G13">
+        <v>0</v>
+      </c>
+      <c r="J13" t="s">
+        <v>26</v>
+      </c>
+      <c r="K13">
+        <v>39.579000000000001</v>
+      </c>
+      <c r="L13" t="s">
+        <v>60</v>
+      </c>
+      <c r="M13" t="s">
+        <v>21</v>
+      </c>
+      <c r="N13" t="s">
+        <v>61</v>
+      </c>
+      <c r="O13" s="3">
+        <v>4.0541666666666663</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A14" s="2">
+        <v>46230.353472222218</v>
+      </c>
+      <c r="B14" s="3">
+        <v>0.97499999999999998</v>
+      </c>
+      <c r="C14" s="2">
+        <v>46225.324305555558</v>
+      </c>
+      <c r="D14">
+        <v>0</v>
+      </c>
+      <c r="E14">
+        <v>23.4</v>
+      </c>
+      <c r="F14" s="3">
+        <v>0</v>
+      </c>
+      <c r="G14">
+        <v>0</v>
+      </c>
+      <c r="J14" t="s">
+        <v>26</v>
+      </c>
+      <c r="K14">
+        <v>39.579000000000001</v>
+      </c>
+      <c r="L14" t="s">
+        <v>60</v>
+      </c>
+      <c r="M14" t="s">
+        <v>21</v>
+      </c>
+      <c r="N14" t="s">
+        <v>61</v>
+      </c>
+      <c r="O14" s="3">
+        <v>5.0291666666666668</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A15" s="2">
+        <v>46230.865972222222</v>
+      </c>
+      <c r="B15" s="3">
+        <v>0.51249999999999996</v>
+      </c>
+      <c r="C15" s="2">
+        <v>46225.324305555558</v>
+      </c>
+      <c r="D15">
+        <v>0</v>
+      </c>
+      <c r="E15">
+        <v>12.3</v>
+      </c>
+      <c r="F15" s="3">
+        <v>0</v>
+      </c>
+      <c r="G15">
+        <v>0</v>
+      </c>
+      <c r="J15" t="s">
+        <v>26</v>
+      </c>
+      <c r="K15">
+        <v>39.579000000000001</v>
+      </c>
+      <c r="L15" t="s">
+        <v>60</v>
+      </c>
+      <c r="M15" t="s">
+        <v>21</v>
+      </c>
+      <c r="N15" t="s">
+        <v>61</v>
+      </c>
+      <c r="O15" s="3">
+        <v>5.541666666666667</v>
       </c>
     </row>
   </sheetData>
@@ -4082,16 +7162,8 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
-  <dimension ref="A1:O8"/>
+  <dimension ref="A1:O15"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="25" customWidth="1"/>
-    <col min="3" max="3" width="23.44140625" customWidth="1"/>
-    <col min="12" max="12" width="25.109375" customWidth="1"/>
-    <col min="13" max="13" width="20.109375" customWidth="1"/>
-    <col min="14" max="14" width="16.77734375" customWidth="1"/>
-    <col min="15" max="15" width="18.88671875" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
@@ -4148,7 +7220,7 @@
         <v>46219.638888888891</v>
       </c>
       <c r="J2" t="s">
-        <v>39</v>
+        <v>50</v>
       </c>
       <c r="O2" s="3">
         <v>0.2305555555555556</v>
@@ -4183,16 +7255,16 @@
         <v>1.54</v>
       </c>
       <c r="J3" t="s">
-        <v>39</v>
+        <v>50</v>
       </c>
       <c r="K3">
         <v>2.2309999999999999</v>
       </c>
       <c r="L3" t="s">
-        <v>46</v>
+        <v>62</v>
       </c>
       <c r="M3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="O3" s="3">
         <v>6.1805555555555558E-2</v>
@@ -4233,10 +7305,10 @@
         <v>75.03</v>
       </c>
       <c r="L4" t="s">
-        <v>47</v>
+        <v>63</v>
       </c>
       <c r="M4" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="O4" s="3">
         <v>-1.3888888888888889E-3</v>
@@ -4271,16 +7343,16 @@
         <v>0.91</v>
       </c>
       <c r="J5" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="K5">
         <v>87.995000000000005</v>
       </c>
       <c r="L5" t="s">
-        <v>48</v>
+        <v>64</v>
       </c>
       <c r="M5" t="s">
-        <v>49</v>
+        <v>65</v>
       </c>
       <c r="O5" s="3">
         <v>2.7777777777777779E-3</v>
@@ -4315,16 +7387,16 @@
         <v>0.76</v>
       </c>
       <c r="J6" t="s">
-        <v>43</v>
+        <v>52</v>
       </c>
       <c r="K6">
         <v>87.338999999999999</v>
       </c>
       <c r="L6" t="s">
-        <v>48</v>
+        <v>64</v>
       </c>
       <c r="M6" t="s">
-        <v>49</v>
+        <v>65</v>
       </c>
       <c r="O6" s="3">
         <v>3.4721643518518521E-3</v>
@@ -4365,10 +7437,10 @@
         <v>1.516</v>
       </c>
       <c r="L7" t="s">
-        <v>50</v>
+        <v>66</v>
       </c>
       <c r="M7" t="s">
-        <v>49</v>
+        <v>65</v>
       </c>
       <c r="O7" s="3">
         <v>0.27986111111111112</v>
@@ -4409,13 +7481,315 @@
         <v>1.5249999999999999</v>
       </c>
       <c r="L8" t="s">
-        <v>50</v>
+        <v>66</v>
       </c>
       <c r="M8" t="s">
-        <v>49</v>
+        <v>65</v>
       </c>
       <c r="O8" s="3">
         <v>0.2277777777777778</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A9" s="2">
+        <v>46226.9</v>
+      </c>
+      <c r="B9" s="3">
+        <v>0.54722222222222228</v>
+      </c>
+      <c r="C9" s="2">
+        <v>46226.643750000003</v>
+      </c>
+      <c r="D9">
+        <v>0.05</v>
+      </c>
+      <c r="E9">
+        <v>13.133333333333329</v>
+      </c>
+      <c r="F9" s="3">
+        <v>0.51875000000000004</v>
+      </c>
+      <c r="G9">
+        <v>12.45</v>
+      </c>
+      <c r="H9">
+        <v>0</v>
+      </c>
+      <c r="I9">
+        <v>0</v>
+      </c>
+      <c r="J9" t="s">
+        <v>23</v>
+      </c>
+      <c r="K9">
+        <v>1.4990000000000001</v>
+      </c>
+      <c r="L9" t="s">
+        <v>66</v>
+      </c>
+      <c r="M9" t="s">
+        <v>65</v>
+      </c>
+      <c r="O9" s="3">
+        <v>0.25624999999999998</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A10" s="2">
+        <v>46227.289583333331</v>
+      </c>
+      <c r="B10" s="3">
+        <v>0.38958333333333328</v>
+      </c>
+      <c r="C10" s="2">
+        <v>46226.643750000003</v>
+      </c>
+      <c r="D10">
+        <v>0</v>
+      </c>
+      <c r="E10">
+        <v>9.35</v>
+      </c>
+      <c r="F10" s="3">
+        <v>0</v>
+      </c>
+      <c r="G10">
+        <v>0</v>
+      </c>
+      <c r="J10" t="s">
+        <v>23</v>
+      </c>
+      <c r="K10">
+        <v>1.4990000000000001</v>
+      </c>
+      <c r="L10" t="s">
+        <v>66</v>
+      </c>
+      <c r="M10" t="s">
+        <v>65</v>
+      </c>
+      <c r="O10" s="3">
+        <v>0.64583333333333337</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A11" s="2">
+        <v>46227.886805555558</v>
+      </c>
+      <c r="B11" s="3">
+        <v>0.59722222222222221</v>
+      </c>
+      <c r="C11" s="2">
+        <v>46227.793055555558</v>
+      </c>
+      <c r="D11">
+        <v>0.28000000000000003</v>
+      </c>
+      <c r="E11">
+        <v>14.33333333333333</v>
+      </c>
+      <c r="F11" s="3">
+        <v>1.149305555555556</v>
+      </c>
+      <c r="G11">
+        <v>27.583333333333329</v>
+      </c>
+      <c r="H11">
+        <v>0.01</v>
+      </c>
+      <c r="I11">
+        <v>0.01</v>
+      </c>
+      <c r="J11" t="s">
+        <v>23</v>
+      </c>
+      <c r="K11">
+        <v>1.218</v>
+      </c>
+      <c r="L11" t="s">
+        <v>66</v>
+      </c>
+      <c r="M11" t="s">
+        <v>65</v>
+      </c>
+      <c r="O11" s="3">
+        <v>9.375E-2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A12" s="2">
+        <v>46228.268055555563</v>
+      </c>
+      <c r="B12" s="3">
+        <v>0.38124999999999998</v>
+      </c>
+      <c r="C12" s="2">
+        <v>46227.978472222218</v>
+      </c>
+      <c r="D12">
+        <v>0.05</v>
+      </c>
+      <c r="E12">
+        <v>9.15</v>
+      </c>
+      <c r="F12" s="3">
+        <v>0.1854166666666667</v>
+      </c>
+      <c r="G12">
+        <v>4.45</v>
+      </c>
+      <c r="H12">
+        <v>0.01</v>
+      </c>
+      <c r="I12">
+        <v>0.01</v>
+      </c>
+      <c r="J12" t="s">
+        <v>23</v>
+      </c>
+      <c r="K12">
+        <v>1.2150000000000001</v>
+      </c>
+      <c r="L12" t="s">
+        <v>66</v>
+      </c>
+      <c r="M12" t="s">
+        <v>65</v>
+      </c>
+      <c r="O12" s="3">
+        <v>0.28958333333333341</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A13" s="2">
+        <v>46229.378472222219</v>
+      </c>
+      <c r="B13" s="3">
+        <v>1.1104166666666671</v>
+      </c>
+      <c r="C13" s="2">
+        <v>46229.37222222222</v>
+      </c>
+      <c r="D13">
+        <v>0.23</v>
+      </c>
+      <c r="E13">
+        <v>26.65</v>
+      </c>
+      <c r="F13" s="3">
+        <v>1.39375</v>
+      </c>
+      <c r="G13">
+        <v>33.450000000000003</v>
+      </c>
+      <c r="H13">
+        <v>0.01</v>
+      </c>
+      <c r="I13">
+        <v>0.01</v>
+      </c>
+      <c r="J13" t="s">
+        <v>23</v>
+      </c>
+      <c r="K13">
+        <v>1.329</v>
+      </c>
+      <c r="L13" t="s">
+        <v>66</v>
+      </c>
+      <c r="M13" t="s">
+        <v>65</v>
+      </c>
+      <c r="O13" s="3">
+        <v>6.2500000000000003E-3</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A14" s="2">
+        <v>46230.353472222218</v>
+      </c>
+      <c r="B14" s="3">
+        <v>0.97499999999999998</v>
+      </c>
+      <c r="C14" s="2">
+        <v>46230.281944444447</v>
+      </c>
+      <c r="D14">
+        <v>0.09</v>
+      </c>
+      <c r="E14">
+        <v>23.4</v>
+      </c>
+      <c r="F14" s="3">
+        <v>0.90972222222222221</v>
+      </c>
+      <c r="G14">
+        <v>21.833333333333329</v>
+      </c>
+      <c r="H14">
+        <v>0</v>
+      </c>
+      <c r="I14">
+        <v>0</v>
+      </c>
+      <c r="J14" t="s">
+        <v>23</v>
+      </c>
+      <c r="K14">
+        <v>1.3380000000000001</v>
+      </c>
+      <c r="L14" t="s">
+        <v>66</v>
+      </c>
+      <c r="M14" t="s">
+        <v>65</v>
+      </c>
+      <c r="O14" s="3">
+        <v>7.1527777777777773E-2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A15" s="2">
+        <v>46230.865972222222</v>
+      </c>
+      <c r="B15" s="3">
+        <v>0.51249999999999996</v>
+      </c>
+      <c r="C15" s="2">
+        <v>46230.783333333333</v>
+      </c>
+      <c r="D15">
+        <v>0.18</v>
+      </c>
+      <c r="E15">
+        <v>12.3</v>
+      </c>
+      <c r="F15" s="3">
+        <v>0.50138888888888888</v>
+      </c>
+      <c r="G15">
+        <v>12.03333333333333</v>
+      </c>
+      <c r="H15">
+        <v>0.01</v>
+      </c>
+      <c r="I15">
+        <v>0.01</v>
+      </c>
+      <c r="J15" t="s">
+        <v>23</v>
+      </c>
+      <c r="K15">
+        <v>1.1970000000000001</v>
+      </c>
+      <c r="L15" t="s">
+        <v>66</v>
+      </c>
+      <c r="M15" t="s">
+        <v>65</v>
+      </c>
+      <c r="O15" s="3">
+        <v>8.2638888888888887E-2</v>
       </c>
     </row>
   </sheetData>
@@ -4425,19 +7799,8 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
-  <dimension ref="A1:O8"/>
+  <dimension ref="A1:O15"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="21.44140625" customWidth="1"/>
-    <col min="2" max="2" width="11.109375" customWidth="1"/>
-    <col min="3" max="3" width="21.5546875" customWidth="1"/>
-    <col min="4" max="4" width="13" customWidth="1"/>
-    <col min="10" max="10" width="22.5546875" customWidth="1"/>
-    <col min="11" max="11" width="20.109375" customWidth="1"/>
-    <col min="12" max="12" width="20.33203125" customWidth="1"/>
-    <col min="13" max="13" width="13.33203125" customWidth="1"/>
-    <col min="14" max="14" width="24.6640625" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
@@ -4494,7 +7857,7 @@
         <v>46219.902083333327</v>
       </c>
       <c r="J2" t="s">
-        <v>51</v>
+        <v>67</v>
       </c>
       <c r="O2" s="3">
         <v>-6.9444444444444447E-4</v>
@@ -4511,7 +7874,7 @@
         <v>46220.644444444442</v>
       </c>
       <c r="D3">
-        <v>8691.9699999999993</v>
+        <v>9.07</v>
       </c>
       <c r="E3">
         <v>17.81666666666667</v>
@@ -4523,25 +7886,25 @@
         <v>17.81666666666667</v>
       </c>
       <c r="H3">
-        <v>487.86</v>
+        <v>0.51</v>
       </c>
       <c r="I3">
-        <v>263.42</v>
+        <v>0.28000000000000003</v>
       </c>
       <c r="J3" t="s">
-        <v>52</v>
+        <v>68</v>
       </c>
       <c r="K3">
-        <v>8327.09</v>
+        <v>0.22800000000000001</v>
       </c>
       <c r="L3" t="s">
-        <v>53</v>
+        <v>43</v>
       </c>
       <c r="M3" t="s">
-        <v>31</v>
+        <v>17</v>
       </c>
       <c r="N3" t="s">
-        <v>54</v>
+        <v>44</v>
       </c>
       <c r="O3" s="3">
         <v>-6.9444444444444447E-4</v>
@@ -4558,7 +7921,7 @@
         <v>46223.716666666667</v>
       </c>
       <c r="D4">
-        <v>8556.43</v>
+        <v>211.88</v>
       </c>
       <c r="E4">
         <v>86.1</v>
@@ -4570,10 +7933,10 @@
         <v>73.733333333333334</v>
       </c>
       <c r="H4">
-        <v>116.05</v>
+        <v>2.87</v>
       </c>
       <c r="I4">
-        <v>62.66</v>
+        <v>1.55</v>
       </c>
       <c r="J4" t="s">
         <v>19</v>
@@ -4582,7 +7945,7 @@
         <v>2.859</v>
       </c>
       <c r="L4" t="s">
-        <v>55</v>
+        <v>69</v>
       </c>
       <c r="M4" t="s">
         <v>21</v>
@@ -4623,13 +7986,13 @@
         <v>0</v>
       </c>
       <c r="J5" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="K5">
         <v>2.8570000000000002</v>
       </c>
       <c r="L5" t="s">
-        <v>55</v>
+        <v>69</v>
       </c>
       <c r="M5" t="s">
         <v>21</v>
@@ -4664,13 +8027,13 @@
         <v>0</v>
       </c>
       <c r="J6" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="K6">
         <v>2.8570000000000002</v>
       </c>
       <c r="L6" t="s">
-        <v>55</v>
+        <v>69</v>
       </c>
       <c r="M6" t="s">
         <v>21</v>
@@ -4711,13 +8074,13 @@
         <v>0</v>
       </c>
       <c r="J7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="K7">
         <v>2.8679999999999999</v>
       </c>
       <c r="L7" t="s">
-        <v>55</v>
+        <v>69</v>
       </c>
       <c r="M7" t="s">
         <v>21</v>
@@ -4758,13 +8121,13 @@
         <v>0.03</v>
       </c>
       <c r="J8" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="K8">
         <v>2.9769999999999999</v>
       </c>
       <c r="L8" t="s">
-        <v>55</v>
+        <v>69</v>
       </c>
       <c r="M8" t="s">
         <v>21</v>
@@ -4774,6 +8137,317 @@
       </c>
       <c r="O8" s="3">
         <v>1.8749999999999999E-2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A9" s="2">
+        <v>46226.9</v>
+      </c>
+      <c r="B9" s="3">
+        <v>0.54722222222222228</v>
+      </c>
+      <c r="C9" s="2">
+        <v>46226.438194444447</v>
+      </c>
+      <c r="D9">
+        <v>4.83</v>
+      </c>
+      <c r="E9">
+        <v>13.133333333333329</v>
+      </c>
+      <c r="F9" s="3">
+        <v>0.1041666666666667</v>
+      </c>
+      <c r="G9">
+        <v>2.5</v>
+      </c>
+      <c r="H9">
+        <v>1.93</v>
+      </c>
+      <c r="I9">
+        <v>1.04</v>
+      </c>
+      <c r="J9" t="s">
+        <v>26</v>
+      </c>
+      <c r="K9">
+        <v>4.5960000000000001</v>
+      </c>
+      <c r="L9" t="s">
+        <v>70</v>
+      </c>
+      <c r="M9" t="s">
+        <v>21</v>
+      </c>
+      <c r="N9" t="s">
+        <v>22</v>
+      </c>
+      <c r="O9" s="3">
+        <v>0.46180555555555558</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A10" s="2">
+        <v>46227.289583333331</v>
+      </c>
+      <c r="B10" s="3">
+        <v>0.38958333333333328</v>
+      </c>
+      <c r="C10" s="2">
+        <v>46226.438194444447</v>
+      </c>
+      <c r="D10">
+        <v>0</v>
+      </c>
+      <c r="E10">
+        <v>9.35</v>
+      </c>
+      <c r="F10" s="3">
+        <v>0</v>
+      </c>
+      <c r="G10">
+        <v>0</v>
+      </c>
+      <c r="J10" t="s">
+        <v>26</v>
+      </c>
+      <c r="K10">
+        <v>4.5960000000000001</v>
+      </c>
+      <c r="L10" t="s">
+        <v>70</v>
+      </c>
+      <c r="M10" t="s">
+        <v>21</v>
+      </c>
+      <c r="N10" t="s">
+        <v>22</v>
+      </c>
+      <c r="O10" s="3">
+        <v>0.85138888888888886</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A11" s="2">
+        <v>46227.886805555558</v>
+      </c>
+      <c r="B11" s="3">
+        <v>0.59722222222222221</v>
+      </c>
+      <c r="C11" s="2">
+        <v>46226.438194444447</v>
+      </c>
+      <c r="D11">
+        <v>0</v>
+      </c>
+      <c r="E11">
+        <v>14.33333333333333</v>
+      </c>
+      <c r="F11" s="3">
+        <v>0</v>
+      </c>
+      <c r="G11">
+        <v>0</v>
+      </c>
+      <c r="J11" t="s">
+        <v>26</v>
+      </c>
+      <c r="K11">
+        <v>4.5960000000000001</v>
+      </c>
+      <c r="L11" t="s">
+        <v>70</v>
+      </c>
+      <c r="M11" t="s">
+        <v>21</v>
+      </c>
+      <c r="N11" t="s">
+        <v>22</v>
+      </c>
+      <c r="O11" s="3">
+        <v>1.4486111111111111</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A12" s="2">
+        <v>46228.268055555563</v>
+      </c>
+      <c r="B12" s="3">
+        <v>0.38124999999999998</v>
+      </c>
+      <c r="C12" s="2">
+        <v>46226.438194444447</v>
+      </c>
+      <c r="D12">
+        <v>0</v>
+      </c>
+      <c r="E12">
+        <v>9.15</v>
+      </c>
+      <c r="F12" s="3">
+        <v>0</v>
+      </c>
+      <c r="G12">
+        <v>0</v>
+      </c>
+      <c r="J12" t="s">
+        <v>26</v>
+      </c>
+      <c r="K12">
+        <v>4.5960000000000001</v>
+      </c>
+      <c r="L12" t="s">
+        <v>70</v>
+      </c>
+      <c r="M12" t="s">
+        <v>21</v>
+      </c>
+      <c r="N12" t="s">
+        <v>22</v>
+      </c>
+      <c r="O12" s="3">
+        <v>1.8298611111111109</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A13" s="2">
+        <v>46229.378472222219</v>
+      </c>
+      <c r="B13" s="3">
+        <v>1.1104166666666671</v>
+      </c>
+      <c r="C13" s="2">
+        <v>46229.374305555553</v>
+      </c>
+      <c r="D13">
+        <v>206.25</v>
+      </c>
+      <c r="E13">
+        <v>26.65</v>
+      </c>
+      <c r="F13" s="3">
+        <v>2.9361111111111109</v>
+      </c>
+      <c r="G13">
+        <v>70.466666666666669</v>
+      </c>
+      <c r="H13">
+        <v>2.93</v>
+      </c>
+      <c r="I13">
+        <v>1.58</v>
+      </c>
+      <c r="J13" t="s">
+        <v>47</v>
+      </c>
+      <c r="K13">
+        <v>3.3000000000000002E-2</v>
+      </c>
+      <c r="L13" t="s">
+        <v>16</v>
+      </c>
+      <c r="M13" t="s">
+        <v>17</v>
+      </c>
+      <c r="N13" t="s">
+        <v>18</v>
+      </c>
+      <c r="O13" s="3">
+        <v>4.1666666666666666E-3</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A14" s="2">
+        <v>46230.353472222218</v>
+      </c>
+      <c r="B14" s="3">
+        <v>0.97499999999999998</v>
+      </c>
+      <c r="C14" s="2">
+        <v>46230.292361111111</v>
+      </c>
+      <c r="D14">
+        <v>39.5</v>
+      </c>
+      <c r="E14">
+        <v>23.4</v>
+      </c>
+      <c r="F14" s="3">
+        <v>0.91805555555555551</v>
+      </c>
+      <c r="G14">
+        <v>22.033333333333331</v>
+      </c>
+      <c r="H14">
+        <v>1.79</v>
+      </c>
+      <c r="I14">
+        <v>0.97</v>
+      </c>
+      <c r="J14" t="s">
+        <v>26</v>
+      </c>
+      <c r="K14">
+        <v>36.703000000000003</v>
+      </c>
+      <c r="L14" t="s">
+        <v>48</v>
+      </c>
+      <c r="M14" t="s">
+        <v>17</v>
+      </c>
+      <c r="N14" t="s">
+        <v>46</v>
+      </c>
+      <c r="O14" s="3">
+        <v>6.1111111111111109E-2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A15" s="2">
+        <v>46230.865972222222</v>
+      </c>
+      <c r="B15" s="3">
+        <v>0.51249999999999996</v>
+      </c>
+      <c r="C15" s="2">
+        <v>46230.666666666657</v>
+      </c>
+      <c r="D15">
+        <v>139.9</v>
+      </c>
+      <c r="E15">
+        <v>12.3</v>
+      </c>
+      <c r="F15" s="3">
+        <v>0.37430555555555561</v>
+      </c>
+      <c r="G15">
+        <v>8.9833333333333325</v>
+      </c>
+      <c r="H15">
+        <v>15.57</v>
+      </c>
+      <c r="I15">
+        <v>8.41</v>
+      </c>
+      <c r="J15" t="s">
+        <v>26</v>
+      </c>
+      <c r="K15">
+        <v>19.802</v>
+      </c>
+      <c r="L15" t="s">
+        <v>27</v>
+      </c>
+      <c r="M15" t="s">
+        <v>21</v>
+      </c>
+      <c r="N15" t="s">
+        <v>22</v>
+      </c>
+      <c r="O15" s="3">
+        <v>0.1993055555555556</v>
       </c>
     </row>
   </sheetData>
@@ -4783,12 +8457,8 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
-  <dimension ref="A1:O7"/>
+  <dimension ref="A1:O14"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="25.21875" customWidth="1"/>
-    <col min="3" max="3" width="22.5546875" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
@@ -4845,7 +8515,7 @@
         <v>46220.651388888888</v>
       </c>
       <c r="J2" t="s">
-        <v>52</v>
+        <v>68</v>
       </c>
       <c r="O2" s="3">
         <v>-6.9444444444444447E-4</v>
@@ -4883,16 +8553,16 @@
         <v>19</v>
       </c>
       <c r="K3">
-        <v>23.056000000000001</v>
+        <v>1.5649999999999999</v>
       </c>
       <c r="L3" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="M3" t="s">
         <v>21</v>
       </c>
       <c r="N3" t="s">
-        <v>22</v>
+        <v>61</v>
       </c>
       <c r="O3" s="3">
         <v>6.9444444444444447E-4</v>
@@ -4927,19 +8597,19 @@
         <v>0.02</v>
       </c>
       <c r="J4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="K4">
-        <v>22.907</v>
+        <v>1.34</v>
       </c>
       <c r="L4" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="M4" t="s">
         <v>21</v>
       </c>
       <c r="N4" t="s">
-        <v>22</v>
+        <v>61</v>
       </c>
       <c r="O4" s="3">
         <v>2.8472222222222222E-2</v>
@@ -4974,19 +8644,19 @@
         <v>0.02</v>
       </c>
       <c r="J5" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="K5">
-        <v>22.786000000000001</v>
+        <v>1.212</v>
       </c>
       <c r="L5" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="M5" t="s">
         <v>21</v>
       </c>
       <c r="N5" t="s">
-        <v>22</v>
+        <v>61</v>
       </c>
       <c r="O5" s="3">
         <v>2.0833275462962961E-2</v>
@@ -5021,19 +8691,19 @@
         <v>0.06</v>
       </c>
       <c r="J6" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="K6">
-        <v>21.523</v>
+        <v>0.62</v>
       </c>
       <c r="L6" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="M6" t="s">
         <v>21</v>
       </c>
       <c r="N6" t="s">
-        <v>22</v>
+        <v>61</v>
       </c>
       <c r="O6" s="3">
         <v>0.15138888888888891</v>
@@ -5068,22 +8738,345 @@
         <v>0.04</v>
       </c>
       <c r="J7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="K7">
-        <v>22.388999999999999</v>
+        <v>0.84899999999999998</v>
       </c>
       <c r="L7" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="M7" t="s">
         <v>21</v>
       </c>
       <c r="N7" t="s">
-        <v>22</v>
+        <v>61</v>
       </c>
       <c r="O7" s="3">
         <v>3.472222222222222E-3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A8" s="2">
+        <v>46226.9</v>
+      </c>
+      <c r="B8" s="3">
+        <v>0.54722222222222228</v>
+      </c>
+      <c r="C8" s="2">
+        <v>46226.427083333343</v>
+      </c>
+      <c r="D8">
+        <v>0.62</v>
+      </c>
+      <c r="E8">
+        <v>13.133333333333329</v>
+      </c>
+      <c r="F8" s="3">
+        <v>7.7777777777777779E-2</v>
+      </c>
+      <c r="G8">
+        <v>1.8666666666666669</v>
+      </c>
+      <c r="H8">
+        <v>0.33</v>
+      </c>
+      <c r="I8">
+        <v>0.18</v>
+      </c>
+      <c r="J8" t="s">
+        <v>33</v>
+      </c>
+      <c r="K8">
+        <v>0.23699999999999999</v>
+      </c>
+      <c r="L8" t="s">
+        <v>60</v>
+      </c>
+      <c r="M8" t="s">
+        <v>21</v>
+      </c>
+      <c r="N8" t="s">
+        <v>61</v>
+      </c>
+      <c r="O8" s="3">
+        <v>0.47291666666666671</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A9" s="2">
+        <v>46227.289583333331</v>
+      </c>
+      <c r="B9" s="3">
+        <v>0.38958333333333328</v>
+      </c>
+      <c r="C9" s="2">
+        <v>46226.427083333343</v>
+      </c>
+      <c r="D9">
+        <v>0</v>
+      </c>
+      <c r="E9">
+        <v>9.35</v>
+      </c>
+      <c r="F9" s="3">
+        <v>0</v>
+      </c>
+      <c r="G9">
+        <v>0</v>
+      </c>
+      <c r="J9" t="s">
+        <v>33</v>
+      </c>
+      <c r="K9">
+        <v>0.23699999999999999</v>
+      </c>
+      <c r="L9" t="s">
+        <v>60</v>
+      </c>
+      <c r="M9" t="s">
+        <v>21</v>
+      </c>
+      <c r="N9" t="s">
+        <v>61</v>
+      </c>
+      <c r="O9" s="3">
+        <v>0.86250000000000004</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A10" s="2">
+        <v>46227.886805555558</v>
+      </c>
+      <c r="B10" s="3">
+        <v>0.59722222222222221</v>
+      </c>
+      <c r="C10" s="2">
+        <v>46226.427083333343</v>
+      </c>
+      <c r="D10">
+        <v>192.98</v>
+      </c>
+      <c r="E10">
+        <v>14.33333333333333</v>
+      </c>
+      <c r="F10" s="3">
+        <v>0</v>
+      </c>
+      <c r="G10">
+        <v>0</v>
+      </c>
+      <c r="H10" t="s">
+        <v>58</v>
+      </c>
+      <c r="I10" t="s">
+        <v>58</v>
+      </c>
+      <c r="J10" t="s">
+        <v>33</v>
+      </c>
+      <c r="K10">
+        <v>26.596</v>
+      </c>
+      <c r="L10" t="s">
+        <v>71</v>
+      </c>
+      <c r="M10" t="s">
+        <v>32</v>
+      </c>
+      <c r="N10" t="s">
+        <v>72</v>
+      </c>
+      <c r="O10" s="3">
+        <v>1.4597222222222219</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A11" s="2">
+        <v>46228.268055555563</v>
+      </c>
+      <c r="B11" s="3">
+        <v>0.38124999999999998</v>
+      </c>
+      <c r="C11" s="2">
+        <v>46228.259027777778</v>
+      </c>
+      <c r="D11">
+        <v>91.64</v>
+      </c>
+      <c r="E11">
+        <v>9.15</v>
+      </c>
+      <c r="F11" s="3">
+        <v>1.8319444444444439</v>
+      </c>
+      <c r="G11">
+        <v>43.966666666666669</v>
+      </c>
+      <c r="H11">
+        <v>2.08</v>
+      </c>
+      <c r="I11">
+        <v>1.1200000000000001</v>
+      </c>
+      <c r="J11" t="s">
+        <v>33</v>
+      </c>
+      <c r="K11">
+        <v>114.65</v>
+      </c>
+      <c r="L11" t="s">
+        <v>71</v>
+      </c>
+      <c r="M11" t="s">
+        <v>32</v>
+      </c>
+      <c r="N11" t="s">
+        <v>72</v>
+      </c>
+      <c r="O11" s="3">
+        <v>9.0277777777777769E-3</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A12" s="2">
+        <v>46229.378472222219</v>
+      </c>
+      <c r="B12" s="3">
+        <v>1.1104166666666671</v>
+      </c>
+      <c r="C12" s="2">
+        <v>46229.375</v>
+      </c>
+      <c r="D12">
+        <v>209.02</v>
+      </c>
+      <c r="E12">
+        <v>26.65</v>
+      </c>
+      <c r="F12" s="3">
+        <v>1.1159722222222219</v>
+      </c>
+      <c r="G12">
+        <v>26.783333333333331</v>
+      </c>
+      <c r="H12">
+        <v>7.8</v>
+      </c>
+      <c r="I12">
+        <v>4.21</v>
+      </c>
+      <c r="J12" t="s">
+        <v>33</v>
+      </c>
+      <c r="K12">
+        <v>1.8009999999999999</v>
+      </c>
+      <c r="L12" t="s">
+        <v>43</v>
+      </c>
+      <c r="M12" t="s">
+        <v>17</v>
+      </c>
+      <c r="N12" t="s">
+        <v>44</v>
+      </c>
+      <c r="O12" s="3">
+        <v>3.472222222222222E-3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A13" s="2">
+        <v>46230.353472222218</v>
+      </c>
+      <c r="B13" s="3">
+        <v>0.97499999999999998</v>
+      </c>
+      <c r="C13" s="2">
+        <v>46230.351388888892</v>
+      </c>
+      <c r="D13">
+        <v>0.1</v>
+      </c>
+      <c r="E13">
+        <v>23.4</v>
+      </c>
+      <c r="F13" s="3">
+        <v>0.97638888888888886</v>
+      </c>
+      <c r="G13">
+        <v>23.43333333333333</v>
+      </c>
+      <c r="H13">
+        <v>0</v>
+      </c>
+      <c r="I13">
+        <v>0</v>
+      </c>
+      <c r="J13" t="s">
+        <v>42</v>
+      </c>
+      <c r="K13">
+        <v>1.8959999999999999</v>
+      </c>
+      <c r="L13" t="s">
+        <v>43</v>
+      </c>
+      <c r="M13" t="s">
+        <v>17</v>
+      </c>
+      <c r="N13" t="s">
+        <v>44</v>
+      </c>
+      <c r="O13" s="3">
+        <v>2.0833333333333329E-3</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A14" s="2">
+        <v>46230.865972222222</v>
+      </c>
+      <c r="B14" s="3">
+        <v>0.51249999999999996</v>
+      </c>
+      <c r="C14" s="2">
+        <v>46230.857638888891</v>
+      </c>
+      <c r="D14">
+        <v>0.02</v>
+      </c>
+      <c r="E14">
+        <v>12.3</v>
+      </c>
+      <c r="F14" s="3">
+        <v>0.50624999999999998</v>
+      </c>
+      <c r="G14">
+        <v>12.15</v>
+      </c>
+      <c r="H14">
+        <v>0</v>
+      </c>
+      <c r="I14">
+        <v>0</v>
+      </c>
+      <c r="J14" t="s">
+        <v>42</v>
+      </c>
+      <c r="K14">
+        <v>1.8779999999999999</v>
+      </c>
+      <c r="L14" t="s">
+        <v>43</v>
+      </c>
+      <c r="M14" t="s">
+        <v>17</v>
+      </c>
+      <c r="N14" t="s">
+        <v>44</v>
+      </c>
+      <c r="O14" s="3">
+        <v>8.3333333333333332E-3</v>
       </c>
     </row>
   </sheetData>
@@ -5093,17 +9086,8 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
-  <dimension ref="A1:O8"/>
+  <dimension ref="A1:O15"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="22.21875" customWidth="1"/>
-    <col min="2" max="2" width="4.33203125" customWidth="1"/>
-    <col min="3" max="3" width="19.6640625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="3.6640625" customWidth="1"/>
-    <col min="12" max="12" width="22.33203125" customWidth="1"/>
-    <col min="13" max="13" width="19" customWidth="1"/>
-    <col min="14" max="14" width="11.44140625" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
@@ -5160,7 +9144,7 @@
         <v>46219</v>
       </c>
       <c r="J2" t="s">
-        <v>51</v>
+        <v>67</v>
       </c>
       <c r="O2" s="3">
         <v>0</v>
@@ -5195,19 +9179,19 @@
         <v>2.5</v>
       </c>
       <c r="J3" t="s">
-        <v>51</v>
+        <v>67</v>
       </c>
       <c r="K3">
         <v>1.006</v>
       </c>
       <c r="L3" t="s">
-        <v>57</v>
+        <v>45</v>
       </c>
       <c r="M3" t="s">
         <v>17</v>
       </c>
       <c r="N3" t="s">
-        <v>58</v>
+        <v>46</v>
       </c>
       <c r="O3" s="3">
         <v>0</v>
@@ -5248,10 +9232,10 @@
         <v>0.5</v>
       </c>
       <c r="L4" t="s">
-        <v>59</v>
+        <v>73</v>
       </c>
       <c r="M4" t="s">
-        <v>49</v>
+        <v>65</v>
       </c>
       <c r="O4" s="3">
         <v>-1.3888888888888889E-3</v>
@@ -5286,16 +9270,16 @@
         <v>0</v>
       </c>
       <c r="J5" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="K5">
         <v>0.496</v>
       </c>
       <c r="L5" t="s">
-        <v>59</v>
+        <v>73</v>
       </c>
       <c r="M5" t="s">
-        <v>49</v>
+        <v>65</v>
       </c>
       <c r="O5" s="3">
         <v>2.7777777777777779E-3</v>
@@ -5330,16 +9314,16 @@
         <v>0</v>
       </c>
       <c r="J6" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="K6">
         <v>0.501</v>
       </c>
       <c r="L6" t="s">
-        <v>59</v>
+        <v>73</v>
       </c>
       <c r="M6" t="s">
-        <v>49</v>
+        <v>65</v>
       </c>
       <c r="O6" s="3">
         <v>4.8610532407407396E-3</v>
@@ -5374,16 +9358,16 @@
         <v>0</v>
       </c>
       <c r="J7" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="K7">
         <v>0.497</v>
       </c>
       <c r="L7" t="s">
-        <v>59</v>
+        <v>73</v>
       </c>
       <c r="M7" t="s">
-        <v>49</v>
+        <v>65</v>
       </c>
       <c r="O7" s="3">
         <v>-5.2777777777777778E-2</v>
@@ -5418,19 +9402,327 @@
         <v>0</v>
       </c>
       <c r="J8" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="K8">
         <v>0.502</v>
       </c>
       <c r="L8" t="s">
-        <v>59</v>
+        <v>73</v>
       </c>
       <c r="M8" t="s">
-        <v>49</v>
+        <v>65</v>
       </c>
       <c r="O8" s="3">
         <v>3.472222222222222E-3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A9" s="2">
+        <v>46226.9</v>
+      </c>
+      <c r="B9" s="3">
+        <v>0.54722222222222228</v>
+      </c>
+      <c r="C9" s="2">
+        <v>46226.897222222222</v>
+      </c>
+      <c r="D9">
+        <v>0.01</v>
+      </c>
+      <c r="E9">
+        <v>13.133333333333329</v>
+      </c>
+      <c r="F9" s="3">
+        <v>0.54791666666666672</v>
+      </c>
+      <c r="G9">
+        <v>13.15</v>
+      </c>
+      <c r="H9">
+        <v>0</v>
+      </c>
+      <c r="I9">
+        <v>0</v>
+      </c>
+      <c r="J9" t="s">
+        <v>47</v>
+      </c>
+      <c r="K9">
+        <v>0.497</v>
+      </c>
+      <c r="L9" t="s">
+        <v>73</v>
+      </c>
+      <c r="M9" t="s">
+        <v>65</v>
+      </c>
+      <c r="O9" s="3">
+        <v>2.7777777777777779E-3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A10" s="2">
+        <v>46227.289583333331</v>
+      </c>
+      <c r="B10" s="3">
+        <v>0.38958333333333328</v>
+      </c>
+      <c r="C10" s="2">
+        <v>46227.286805555559</v>
+      </c>
+      <c r="D10">
+        <v>0.01</v>
+      </c>
+      <c r="E10">
+        <v>9.35</v>
+      </c>
+      <c r="F10" s="3">
+        <v>0.38958333333333328</v>
+      </c>
+      <c r="G10">
+        <v>9.35</v>
+      </c>
+      <c r="H10">
+        <v>0</v>
+      </c>
+      <c r="I10">
+        <v>0</v>
+      </c>
+      <c r="J10" t="s">
+        <v>47</v>
+      </c>
+      <c r="K10">
+        <v>0.498</v>
+      </c>
+      <c r="L10" t="s">
+        <v>73</v>
+      </c>
+      <c r="M10" t="s">
+        <v>65</v>
+      </c>
+      <c r="O10" s="3">
+        <v>2.7777777777777779E-3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A11" s="2">
+        <v>46227.886805555558</v>
+      </c>
+      <c r="B11" s="3">
+        <v>0.59722222222222221</v>
+      </c>
+      <c r="C11" s="2">
+        <v>46227.882638888892</v>
+      </c>
+      <c r="D11">
+        <v>0</v>
+      </c>
+      <c r="E11">
+        <v>14.33333333333333</v>
+      </c>
+      <c r="F11" s="3">
+        <v>0.59583333333333333</v>
+      </c>
+      <c r="G11">
+        <v>14.3</v>
+      </c>
+      <c r="H11">
+        <v>0</v>
+      </c>
+      <c r="I11">
+        <v>0</v>
+      </c>
+      <c r="J11" t="s">
+        <v>47</v>
+      </c>
+      <c r="K11">
+        <v>0.501</v>
+      </c>
+      <c r="L11" t="s">
+        <v>73</v>
+      </c>
+      <c r="M11" t="s">
+        <v>65</v>
+      </c>
+      <c r="O11" s="3">
+        <v>4.1666666666666666E-3</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A12" s="2">
+        <v>46228.268055555563</v>
+      </c>
+      <c r="B12" s="3">
+        <v>0.38124999999999998</v>
+      </c>
+      <c r="C12" s="2">
+        <v>46228.268055555563</v>
+      </c>
+      <c r="D12">
+        <v>0.01</v>
+      </c>
+      <c r="E12">
+        <v>9.15</v>
+      </c>
+      <c r="F12" s="3">
+        <v>0.38541666666666669</v>
+      </c>
+      <c r="G12">
+        <v>9.25</v>
+      </c>
+      <c r="H12">
+        <v>0</v>
+      </c>
+      <c r="I12">
+        <v>0</v>
+      </c>
+      <c r="J12" t="s">
+        <v>47</v>
+      </c>
+      <c r="K12">
+        <v>0.498</v>
+      </c>
+      <c r="L12" t="s">
+        <v>73</v>
+      </c>
+      <c r="M12" t="s">
+        <v>65</v>
+      </c>
+      <c r="O12" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A13" s="2">
+        <v>46229.378472222219</v>
+      </c>
+      <c r="B13" s="3">
+        <v>1.1104166666666671</v>
+      </c>
+      <c r="C13" s="2">
+        <v>46229.375</v>
+      </c>
+      <c r="D13">
+        <v>0.01</v>
+      </c>
+      <c r="E13">
+        <v>26.65</v>
+      </c>
+      <c r="F13" s="3">
+        <v>1.106944444444445</v>
+      </c>
+      <c r="G13">
+        <v>26.56666666666667</v>
+      </c>
+      <c r="H13">
+        <v>0</v>
+      </c>
+      <c r="I13">
+        <v>0</v>
+      </c>
+      <c r="J13" t="s">
+        <v>47</v>
+      </c>
+      <c r="K13">
+        <v>0.499</v>
+      </c>
+      <c r="L13" t="s">
+        <v>73</v>
+      </c>
+      <c r="M13" t="s">
+        <v>65</v>
+      </c>
+      <c r="O13" s="3">
+        <v>3.472222222222222E-3</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A14" s="2">
+        <v>46230.353472222218</v>
+      </c>
+      <c r="B14" s="3">
+        <v>0.97499999999999998</v>
+      </c>
+      <c r="C14" s="2">
+        <v>46230.347916666673</v>
+      </c>
+      <c r="D14">
+        <v>0.01</v>
+      </c>
+      <c r="E14">
+        <v>23.4</v>
+      </c>
+      <c r="F14" s="3">
+        <v>0.97291666666666665</v>
+      </c>
+      <c r="G14">
+        <v>23.35</v>
+      </c>
+      <c r="H14">
+        <v>0</v>
+      </c>
+      <c r="I14">
+        <v>0</v>
+      </c>
+      <c r="J14" t="s">
+        <v>47</v>
+      </c>
+      <c r="K14">
+        <v>0.498</v>
+      </c>
+      <c r="L14" t="s">
+        <v>73</v>
+      </c>
+      <c r="M14" t="s">
+        <v>65</v>
+      </c>
+      <c r="O14" s="3">
+        <v>5.5555555555555558E-3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A15" s="2">
+        <v>46230.865972222222</v>
+      </c>
+      <c r="B15" s="3">
+        <v>0.51249999999999996</v>
+      </c>
+      <c r="C15" s="2">
+        <v>46230.85833333333</v>
+      </c>
+      <c r="D15">
+        <v>0</v>
+      </c>
+      <c r="E15">
+        <v>12.3</v>
+      </c>
+      <c r="F15" s="3">
+        <v>0.51041666666666663</v>
+      </c>
+      <c r="G15">
+        <v>12.25</v>
+      </c>
+      <c r="H15">
+        <v>0</v>
+      </c>
+      <c r="I15">
+        <v>0</v>
+      </c>
+      <c r="J15" t="s">
+        <v>47</v>
+      </c>
+      <c r="K15">
+        <v>0.496</v>
+      </c>
+      <c r="L15" t="s">
+        <v>73</v>
+      </c>
+      <c r="M15" t="s">
+        <v>65</v>
+      </c>
+      <c r="O15" s="3">
+        <v>7.6388888888888886E-3</v>
       </c>
     </row>
   </sheetData>
